--- a/Step4-RunTestCase/final-data/cross_categorized_results.xlsx
+++ b/Step4-RunTestCase/final-data/cross_categorized_results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="cross_categorized_results" sheetId="1" r:id="rId1"/>
@@ -4372,13 +4372,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F353"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="48.375" customWidth="1"/>
-    <col min="3" max="3" width="33.25" customWidth="1"/>
-    <col min="4" max="4" width="65.75" customWidth="1"/>
-    <col min="5" max="5" width="36.125" customWidth="1"/>
-    <col min="6" max="6" width="98.625" customWidth="1"/>
+    <col min="1" max="1" width="48.3727272727273" customWidth="1"/>
+    <col min="3" max="3" width="33.2545454545455" customWidth="1"/>
+    <col min="4" max="4" width="65.7545454545455" customWidth="1"/>
+    <col min="5" max="5" width="36.1272727272727" customWidth="1"/>
+    <col min="6" max="6" width="98.6272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4401,7 +4401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="54" spans="1:6">
+    <row r="2" ht="168" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="108" spans="1:6">
+    <row r="3" ht="112" spans="1:6">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="108" spans="1:6">
+    <row r="4" ht="112" spans="1:6">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" ht="67.5" spans="1:6">
+    <row r="5" ht="224" spans="1:6">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" ht="40.5" spans="1:6">
+    <row r="6" ht="168" spans="1:6">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" ht="54" spans="1:6">
+    <row r="7" ht="182" spans="1:6">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" ht="40.5" spans="1:6">
+    <row r="8" ht="42" spans="1:6">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" ht="94.5" spans="1:6">
+    <row r="9" ht="98" spans="1:6">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" ht="108" spans="1:6">
+    <row r="10" ht="112" spans="1:6">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="108" spans="1:6">
+    <row r="11" ht="112" spans="1:6">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" ht="121.5" spans="1:6">
+    <row r="12" ht="126" spans="1:6">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" ht="81" spans="1:6">
+    <row r="13" ht="84" spans="1:6">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" ht="27" spans="1:6">
+    <row r="14" ht="56" spans="1:6">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" ht="27" spans="1:6">
+    <row r="15" ht="42" spans="1:6">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" ht="121.5" spans="1:6">
+    <row r="16" ht="126" spans="1:6">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" ht="54" spans="1:6">
+    <row r="17" ht="210" spans="1:6">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" ht="27" spans="1:6">
+    <row r="18" ht="42" spans="1:6">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" ht="81" spans="1:6">
+    <row r="19" ht="84" spans="1:6">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" ht="135" spans="1:6">
+    <row r="20" ht="140" spans="1:6">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" ht="54" spans="1:6">
+    <row r="21" ht="182" spans="1:6">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" ht="54" spans="1:6">
+    <row r="22" ht="182" spans="1:6">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" ht="54" spans="1:6">
+    <row r="23" ht="182" spans="1:6">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" ht="121.5" spans="1:6">
+    <row r="24" ht="126" spans="1:6">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" ht="54" spans="1:6">
+    <row r="25" ht="210" spans="1:6">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" ht="54" spans="1:6">
+    <row r="26" ht="182" spans="1:6">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" ht="108" spans="1:6">
+    <row r="28" ht="112" spans="1:6">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" ht="121.5" spans="1:6">
+    <row r="29" ht="126" spans="1:6">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" ht="148.5" spans="1:6">
+    <row r="30" ht="154" spans="1:6">
       <c r="A30" t="s">
         <v>73</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" ht="148.5" spans="1:6">
+    <row r="31" ht="154" spans="1:6">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" ht="27" spans="1:6">
+    <row r="32" ht="28" spans="1:6">
       <c r="A32" t="s">
         <v>77</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" ht="27" spans="1:6">
+    <row r="33" ht="56" spans="1:6">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -4957,7 +4957,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" ht="148.5" spans="1:6">
+    <row r="34" ht="154" spans="1:6">
       <c r="A34" t="s">
         <v>81</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" ht="148.5" spans="1:6">
+    <row r="35" ht="154" spans="1:6">
       <c r="A35" t="s">
         <v>83</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="36" ht="121.5" spans="1:6">
+    <row r="36" ht="126" spans="1:6">
       <c r="A36" t="s">
         <v>86</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" ht="40.5" spans="1:6">
+    <row r="37" ht="42" spans="1:6">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" ht="54" spans="1:6">
+    <row r="38" ht="182" spans="1:6">
       <c r="A38" t="s">
         <v>90</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" ht="54" spans="1:6">
+    <row r="39" ht="182" spans="1:6">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" ht="40.5" spans="1:6">
+    <row r="40" ht="70" spans="1:6">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" ht="81" spans="1:6">
+    <row r="41" ht="84" spans="1:6">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" ht="27" spans="1:6">
+    <row r="42" ht="28" spans="1:6">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" ht="121.5" spans="1:6">
+    <row r="43" ht="126" spans="1:6">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" ht="81" spans="1:6">
+    <row r="44" ht="84" spans="1:6">
       <c r="A44" t="s">
         <v>100</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" ht="121.5" spans="1:6">
+    <row r="45" ht="126" spans="1:6">
       <c r="A45" t="s">
         <v>101</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" ht="27" spans="1:6">
+    <row r="47" ht="28" spans="1:6">
       <c r="A47" t="s">
         <v>104</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" ht="81" spans="1:6">
+    <row r="48" ht="84" spans="1:6">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" ht="54" spans="1:6">
+    <row r="49" ht="182" spans="1:6">
       <c r="A49" t="s">
         <v>106</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="50" ht="27" spans="1:6">
+    <row r="50" ht="56" spans="1:6">
       <c r="A50" t="s">
         <v>108</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="51" ht="27" spans="1:6">
+    <row r="51" ht="70" spans="1:6">
       <c r="A51" t="s">
         <v>110</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" ht="27" spans="1:6">
+    <row r="52" ht="42" spans="1:6">
       <c r="A52" t="s">
         <v>112</v>
       </c>
@@ -5277,7 +5277,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="53" ht="27" spans="1:6">
+    <row r="53" ht="70" spans="1:6">
       <c r="A53" t="s">
         <v>114</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="54" ht="135" spans="1:6">
+    <row r="54" ht="140" spans="1:6">
       <c r="A54" t="s">
         <v>116</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="55" ht="81" spans="1:6">
+    <row r="55" ht="84" spans="1:6">
       <c r="A55" t="s">
         <v>118</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" ht="81" spans="1:6">
+    <row r="56" ht="84" spans="1:6">
       <c r="A56" t="s">
         <v>119</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" ht="135" spans="1:6">
+    <row r="57" ht="140" spans="1:6">
       <c r="A57" t="s">
         <v>120</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="58" ht="67.5" spans="1:6">
+    <row r="58" ht="224" spans="1:6">
       <c r="A58" t="s">
         <v>122</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="59" ht="81" spans="1:6">
+    <row r="59" ht="84" spans="1:6">
       <c r="A59" t="s">
         <v>124</v>
       </c>
@@ -5396,7 +5396,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="60" ht="81" spans="1:6">
+    <row r="60" ht="84" spans="1:6">
       <c r="A60" t="s">
         <v>125</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" ht="135" spans="1:6">
+    <row r="61" ht="140" spans="1:6">
       <c r="A61" t="s">
         <v>126</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="62" ht="135" spans="1:6">
+    <row r="62" ht="140" spans="1:6">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="63" ht="81" spans="1:6">
+    <row r="63" ht="84" spans="1:6">
       <c r="A63" t="s">
         <v>130</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" ht="54" spans="1:6">
+    <row r="64" ht="182" spans="1:6">
       <c r="A64" t="s">
         <v>131</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="65" ht="135" spans="1:6">
+    <row r="65" ht="140" spans="1:6">
       <c r="A65" t="s">
         <v>133</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="66" ht="121.5" spans="1:6">
+    <row r="66" ht="126" spans="1:6">
       <c r="A66" t="s">
         <v>135</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="67" ht="135" spans="1:6">
+    <row r="67" ht="140" spans="1:6">
       <c r="A67" t="s">
         <v>138</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="68" ht="135" spans="1:6">
+    <row r="68" ht="140" spans="1:6">
       <c r="A68" t="s">
         <v>140</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="69" ht="81" spans="1:6">
+    <row r="69" ht="84" spans="1:6">
       <c r="A69" t="s">
         <v>142</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="70" ht="27" spans="1:6">
+    <row r="70" ht="56" spans="1:6">
       <c r="A70" t="s">
         <v>144</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="71" ht="54" spans="1:6">
+    <row r="71" ht="168" spans="1:6">
       <c r="A71" t="s">
         <v>146</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="72" ht="108" spans="1:6">
+    <row r="72" ht="112" spans="1:6">
       <c r="A72" t="s">
         <v>148</v>
       </c>
@@ -5620,7 +5620,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="73" ht="40.5" spans="1:6">
+    <row r="73" ht="84" spans="1:6">
       <c r="A73" t="s">
         <v>150</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" ht="27" spans="1:6">
+    <row r="75" ht="56" spans="1:6">
       <c r="A75" t="s">
         <v>153</v>
       </c>
@@ -5682,7 +5682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" ht="81" spans="1:6">
+    <row r="77" ht="84" spans="1:6">
       <c r="A77" t="s">
         <v>156</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" ht="27" spans="1:6">
+    <row r="78" ht="28" spans="1:6">
       <c r="A78" t="s">
         <v>158</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="80" ht="108" spans="1:6">
+    <row r="80" ht="112" spans="1:6">
       <c r="A80" t="s">
         <v>162</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="81" ht="108" spans="1:6">
+    <row r="81" ht="112" spans="1:6">
       <c r="A81" t="s">
         <v>164</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="82" ht="108" spans="1:6">
+    <row r="82" ht="112" spans="1:6">
       <c r="A82" t="s">
         <v>168</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="83" ht="108" spans="1:6">
+    <row r="83" ht="112" spans="1:6">
       <c r="A83" t="s">
         <v>170</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" ht="27" spans="1:6">
+    <row r="85" ht="42" spans="1:6">
       <c r="A85" t="s">
         <v>174</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="86" ht="108" spans="1:6">
+    <row r="86" ht="112" spans="1:6">
       <c r="A86" t="s">
         <v>176</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="87" ht="81" spans="1:6">
+    <row r="87" ht="84" spans="1:6">
       <c r="A87" t="s">
         <v>178</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" ht="81" spans="1:6">
+    <row r="88" ht="84" spans="1:6">
       <c r="A88" t="s">
         <v>179</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="89" ht="81" spans="1:6">
+    <row r="89" ht="84" spans="1:6">
       <c r="A89" t="s">
         <v>180</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="90" ht="81" spans="1:6">
+    <row r="90" ht="84" spans="1:6">
       <c r="A90" t="s">
         <v>181</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="91" ht="81" spans="1:6">
+    <row r="91" ht="84" spans="1:6">
       <c r="A91" t="s">
         <v>182</v>
       </c>
@@ -5946,7 +5946,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" ht="81" spans="1:6">
+    <row r="92" ht="84" spans="1:6">
       <c r="A92" t="s">
         <v>183</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" ht="81" spans="1:6">
+    <row r="94" ht="84" spans="1:6">
       <c r="A94" t="s">
         <v>185</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="95" ht="81" spans="1:6">
+    <row r="95" ht="84" spans="1:6">
       <c r="A95" t="s">
         <v>186</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="96" ht="81" spans="1:6">
+    <row r="96" ht="84" spans="1:6">
       <c r="A96" t="s">
         <v>188</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="97" ht="54" spans="1:6">
+    <row r="97" ht="168" spans="1:6">
       <c r="A97" t="s">
         <v>189</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="98" ht="121.5" spans="1:6">
+    <row r="98" ht="126" spans="1:6">
       <c r="A98" t="s">
         <v>191</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="99" ht="54" spans="1:6">
+    <row r="99" ht="182" spans="1:6">
       <c r="A99" t="s">
         <v>193</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="100" ht="108" spans="1:6">
+    <row r="100" ht="112" spans="1:6">
       <c r="A100" t="s">
         <v>195</v>
       </c>
@@ -6096,7 +6096,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="101" ht="67.5" spans="1:6">
+    <row r="101" ht="210" spans="1:6">
       <c r="A101" t="s">
         <v>197</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="102" ht="108" spans="1:6">
+    <row r="102" ht="112" spans="1:6">
       <c r="A102" t="s">
         <v>199</v>
       </c>
@@ -6133,7 +6133,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="103" ht="54" spans="1:6">
+    <row r="103" ht="182" spans="1:6">
       <c r="A103" t="s">
         <v>202</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="104" ht="54" spans="1:6">
+    <row r="104" ht="210" spans="1:6">
       <c r="A104" t="s">
         <v>204</v>
       </c>
@@ -6167,7 +6167,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="105" ht="108" spans="1:6">
+    <row r="105" ht="112" spans="1:6">
       <c r="A105" t="s">
         <v>206</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="106" ht="108" spans="1:6">
+    <row r="106" ht="112" spans="1:6">
       <c r="A106" t="s">
         <v>208</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="107" ht="121.5" spans="1:6">
+    <row r="107" ht="126" spans="1:6">
       <c r="A107" t="s">
         <v>210</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="108" ht="40.5" spans="1:6">
+    <row r="108" ht="154" spans="1:6">
       <c r="A108" t="s">
         <v>212</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="109" ht="121.5" spans="1:6">
+    <row r="109" ht="126" spans="1:6">
       <c r="A109" t="s">
         <v>214</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="110" ht="54" spans="1:6">
+    <row r="110" ht="182" spans="1:6">
       <c r="A110" t="s">
         <v>216</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="111" ht="54" spans="1:6">
+    <row r="111" ht="182" spans="1:6">
       <c r="A111" t="s">
         <v>218</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="112" ht="54" spans="1:6">
+    <row r="112" ht="168" spans="1:6">
       <c r="A112" t="s">
         <v>220</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" ht="108" spans="1:6">
+    <row r="113" ht="112" spans="1:6">
       <c r="A113" t="s">
         <v>221</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="114" ht="121.5" spans="1:6">
+    <row r="114" ht="280" spans="1:6">
       <c r="A114" t="s">
         <v>223</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="115" ht="54" spans="1:6">
+    <row r="115" ht="182" spans="1:6">
       <c r="A115" t="s">
         <v>226</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="116" ht="81" spans="1:6">
+    <row r="116" ht="84" spans="1:6">
       <c r="A116" t="s">
         <v>228</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="117" ht="121.5" spans="1:6">
+    <row r="117" ht="126" spans="1:6">
       <c r="A117" t="s">
         <v>230</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="118" ht="94.5" spans="1:6">
+    <row r="118" ht="98" spans="1:6">
       <c r="A118" t="s">
         <v>232</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="119" ht="54" spans="1:6">
+    <row r="119" ht="196" spans="1:6">
       <c r="A119" t="s">
         <v>235</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="120" ht="54" spans="1:6">
+    <row r="120" ht="196" spans="1:6">
       <c r="A120" t="s">
         <v>237</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="121" ht="54" spans="1:6">
+    <row r="121" ht="196" spans="1:6">
       <c r="A121" t="s">
         <v>239</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="122" ht="54" spans="1:6">
+    <row r="122" ht="182" spans="1:6">
       <c r="A122" t="s">
         <v>241</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="123" ht="108" spans="1:6">
+    <row r="123" ht="112" spans="1:6">
       <c r="A123" t="s">
         <v>243</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="124" ht="108" spans="1:6">
+    <row r="124" ht="112" spans="1:6">
       <c r="A124" t="s">
         <v>245</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="125" ht="54" spans="1:6">
+    <row r="125" ht="168" spans="1:6">
       <c r="A125" t="s">
         <v>247</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="126" ht="108" spans="1:6">
+    <row r="126" ht="112" spans="1:6">
       <c r="A126" t="s">
         <v>249</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="127" ht="54" spans="1:6">
+    <row r="127" ht="168" spans="1:6">
       <c r="A127" t="s">
         <v>251</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="128" ht="94.5" spans="1:6">
+    <row r="128" ht="126" spans="1:6">
       <c r="A128" t="s">
         <v>252</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="129" ht="81" spans="1:6">
+    <row r="129" ht="84" spans="1:6">
       <c r="A129" t="s">
         <v>254</v>
       </c>
@@ -6595,7 +6595,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" ht="54" spans="1:6">
+    <row r="130" ht="182" spans="1:6">
       <c r="A130" t="s">
         <v>255</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="131" ht="54" spans="1:6">
+    <row r="131" ht="182" spans="1:6">
       <c r="A131" t="s">
         <v>257</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="132" ht="54" spans="1:6">
+    <row r="132" ht="168" spans="1:6">
       <c r="A132" t="s">
         <v>259</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" ht="94.5" spans="1:6">
+    <row r="133" ht="98" spans="1:6">
       <c r="A133" t="s">
         <v>260</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="134" ht="108" spans="1:6">
+    <row r="134" ht="112" spans="1:6">
       <c r="A134" t="s">
         <v>263</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="135" ht="54" spans="1:6">
+    <row r="135" ht="168" spans="1:6">
       <c r="A135" t="s">
         <v>266</v>
       </c>
@@ -6703,7 +6703,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="136" ht="94.5" spans="1:6">
+    <row r="136" ht="154" spans="1:6">
       <c r="A136" t="s">
         <v>268</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="137" ht="94.5" spans="1:6">
+    <row r="137" ht="112" spans="1:6">
       <c r="A137" t="s">
         <v>271</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="138" ht="378" spans="1:6">
+    <row r="138" ht="406" spans="1:6">
       <c r="A138" t="s">
         <v>273</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" ht="81" spans="1:6">
+    <row r="139" ht="84" spans="1:6">
       <c r="A139" t="s">
         <v>276</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="140" ht="108" spans="1:6">
+    <row r="140" ht="112" spans="1:6">
       <c r="A140" t="s">
         <v>278</v>
       </c>
@@ -6797,7 +6797,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="141" ht="108" spans="1:6">
+    <row r="141" ht="112" spans="1:6">
       <c r="A141" t="s">
         <v>280</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" ht="108" spans="1:6">
+    <row r="142" ht="112" spans="1:6">
       <c r="A142" t="s">
         <v>282</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="143" ht="108" spans="1:6">
+    <row r="143" ht="112" spans="1:6">
       <c r="A143" t="s">
         <v>285</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="144" ht="108" spans="1:6">
+    <row r="144" ht="112" spans="1:6">
       <c r="A144" t="s">
         <v>287</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="145" ht="108" spans="1:6">
+    <row r="145" ht="112" spans="1:6">
       <c r="A145" t="s">
         <v>289</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="146" ht="121.5" spans="1:6">
+    <row r="146" ht="126" spans="1:6">
       <c r="A146" t="s">
         <v>292</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="147" ht="40.5" spans="1:6">
+    <row r="147" ht="84" spans="1:6">
       <c r="A147" t="s">
         <v>294</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="148" ht="54" spans="1:6">
+    <row r="148" ht="196" spans="1:6">
       <c r="A148" t="s">
         <v>296</v>
       </c>
@@ -6939,7 +6939,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="149" ht="40.5" spans="1:6">
+    <row r="149" ht="98" spans="1:6">
       <c r="A149" t="s">
         <v>298</v>
       </c>
@@ -6956,7 +6956,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="150" ht="40.5" spans="1:6">
+    <row r="150" ht="84" spans="1:6">
       <c r="A150" t="s">
         <v>300</v>
       </c>
@@ -6973,7 +6973,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="151" ht="54" spans="1:6">
+    <row r="151" ht="196" spans="1:6">
       <c r="A151" t="s">
         <v>302</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="152" ht="40.5" spans="1:6">
+    <row r="152" ht="154" spans="1:6">
       <c r="A152" t="s">
         <v>304</v>
       </c>
@@ -7007,7 +7007,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="153" ht="135" spans="1:6">
+    <row r="153" ht="140" spans="1:6">
       <c r="A153" t="s">
         <v>306</v>
       </c>
@@ -7027,7 +7027,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="154" ht="54" spans="1:6">
+    <row r="154" ht="182" spans="1:6">
       <c r="A154" t="s">
         <v>309</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="155" ht="108" spans="1:6">
+    <row r="155" ht="112" spans="1:6">
       <c r="A155" t="s">
         <v>311</v>
       </c>
@@ -7061,7 +7061,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="156" ht="54" spans="1:6">
+    <row r="156" ht="168" spans="1:6">
       <c r="A156" t="s">
         <v>313</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="157" ht="27" spans="1:6">
+    <row r="157" ht="42" spans="1:6">
       <c r="A157" t="s">
         <v>315</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="158" ht="27" spans="1:6">
+    <row r="158" ht="56" spans="1:6">
       <c r="A158" t="s">
         <v>317</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="159" ht="27" spans="1:6">
+    <row r="159" ht="56" spans="1:6">
       <c r="A159" t="s">
         <v>319</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="160" ht="27" spans="1:6">
+    <row r="160" ht="56" spans="1:6">
       <c r="A160" t="s">
         <v>321</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="161" ht="27" spans="1:6">
+    <row r="161" ht="42" spans="1:6">
       <c r="A161" t="s">
         <v>323</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="162" ht="27" spans="1:6">
+    <row r="162" ht="42" spans="1:6">
       <c r="A162" t="s">
         <v>325</v>
       </c>
@@ -7180,7 +7180,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="163" ht="27" spans="1:6">
+    <row r="163" ht="56" spans="1:6">
       <c r="A163" t="s">
         <v>327</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="164" ht="27" spans="1:6">
+    <row r="164" ht="56" spans="1:6">
       <c r="A164" t="s">
         <v>329</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="165" ht="81" spans="1:6">
+    <row r="165" ht="84" spans="1:6">
       <c r="A165" t="s">
         <v>330</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="166" ht="27" spans="1:6">
+    <row r="166" ht="42" spans="1:6">
       <c r="A166" t="s">
         <v>331</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" ht="67.5" spans="1:6">
+    <row r="167" ht="224" spans="1:6">
       <c r="A167" t="s">
         <v>333</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="168" ht="54" spans="1:6">
+    <row r="168" ht="168" spans="1:6">
       <c r="A168" t="s">
         <v>335</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" ht="54" spans="1:6">
+    <row r="169" ht="196" spans="1:6">
       <c r="A169" t="s">
         <v>336</v>
       </c>
@@ -7299,7 +7299,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="170" ht="54" spans="1:6">
+    <row r="170" ht="168" spans="1:6">
       <c r="A170" t="s">
         <v>338</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="171" ht="54" spans="1:6">
+    <row r="171" ht="182" spans="1:6">
       <c r="A171" t="s">
         <v>340</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="172" ht="108" spans="1:6">
+    <row r="172" ht="112" spans="1:6">
       <c r="A172" t="s">
         <v>342</v>
       </c>
@@ -7350,7 +7350,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="173" ht="54" spans="1:6">
+    <row r="173" ht="182" spans="1:6">
       <c r="A173" t="s">
         <v>344</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="174" ht="108" spans="1:6">
+    <row r="174" ht="112" spans="1:6">
       <c r="A174" t="s">
         <v>346</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" ht="108" spans="1:6">
+    <row r="175" ht="112" spans="1:6">
       <c r="A175" t="s">
         <v>348</v>
       </c>
@@ -7401,7 +7401,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="176" ht="54" spans="1:6">
+    <row r="176" ht="196" spans="1:6">
       <c r="A176" t="s">
         <v>350</v>
       </c>
@@ -7418,7 +7418,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="177" ht="54" spans="1:6">
+    <row r="177" ht="196" spans="1:6">
       <c r="A177" t="s">
         <v>352</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178" ht="54" spans="1:6">
+    <row r="178" ht="182" spans="1:6">
       <c r="A178" t="s">
         <v>354</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="179" ht="108" spans="1:6">
+    <row r="179" ht="266" spans="1:6">
       <c r="A179" t="s">
         <v>356</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" ht="27" spans="1:6">
+    <row r="180" ht="56" spans="1:6">
       <c r="A180" t="s">
         <v>359</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="181" ht="108" spans="1:6">
+    <row r="181" ht="112" spans="1:6">
       <c r="A181" t="s">
         <v>361</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="182" ht="40.5" spans="1:6">
+    <row r="182" ht="70" spans="1:6">
       <c r="A182" t="s">
         <v>364</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="183" ht="27" spans="1:6">
+    <row r="183" ht="70" spans="1:6">
       <c r="A183" t="s">
         <v>366</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="184" ht="54" spans="1:6">
+    <row r="184" ht="182" spans="1:6">
       <c r="A184" t="s">
         <v>368</v>
       </c>
@@ -7560,7 +7560,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="185" ht="54" spans="1:6">
+    <row r="185" ht="182" spans="1:6">
       <c r="A185" t="s">
         <v>370</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="186" ht="108" spans="1:6">
+    <row r="186" ht="112" spans="1:6">
       <c r="A186" t="s">
         <v>372</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="187" ht="40.5" spans="1:6">
+    <row r="187" ht="56" spans="1:6">
       <c r="A187" t="s">
         <v>374</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="188" ht="27" spans="1:6">
+    <row r="188" ht="42" spans="1:6">
       <c r="A188" t="s">
         <v>376</v>
       </c>
@@ -7628,7 +7628,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="189" ht="54" spans="1:6">
+    <row r="189" ht="182" spans="1:6">
       <c r="A189" t="s">
         <v>378</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="190" ht="54" spans="1:6">
+    <row r="190" ht="196" spans="1:6">
       <c r="A190" t="s">
         <v>380</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="191" ht="40.5" spans="1:6">
+    <row r="191" ht="70" spans="1:6">
       <c r="A191" t="s">
         <v>382</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="192" ht="67.5" spans="1:6">
+    <row r="192" ht="154" spans="1:6">
       <c r="A192" t="s">
         <v>384</v>
       </c>
@@ -7696,7 +7696,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="193" ht="40.5" spans="1:6">
+    <row r="193" ht="154" spans="1:6">
       <c r="A193" t="s">
         <v>386</v>
       </c>
@@ -7713,7 +7713,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="194" ht="54" spans="1:6">
+    <row r="194" ht="70" spans="1:6">
       <c r="A194" t="s">
         <v>388</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="195" ht="27" spans="1:6">
+    <row r="195" ht="56" spans="1:6">
       <c r="A195" t="s">
         <v>391</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="196" ht="81" spans="1:6">
+    <row r="196" ht="84" spans="1:6">
       <c r="A196" t="s">
         <v>393</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="197" ht="40.5" spans="1:6">
+    <row r="197" ht="154" spans="1:6">
       <c r="A197" t="s">
         <v>394</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="198" ht="27" spans="1:6">
+    <row r="198" ht="42" spans="1:6">
       <c r="A198" t="s">
         <v>396</v>
       </c>
@@ -7801,7 +7801,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="199" ht="81" spans="1:6">
+    <row r="199" ht="84" spans="1:6">
       <c r="A199" t="s">
         <v>398</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200" ht="40.5" spans="1:6">
+    <row r="200" ht="70" spans="1:6">
       <c r="A200" t="s">
         <v>399</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="201" ht="54" spans="1:6">
+    <row r="201" ht="182" spans="1:6">
       <c r="A201" t="s">
         <v>401</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="202" ht="27" spans="1:6">
+    <row r="202" ht="42" spans="1:6">
       <c r="A202" t="s">
         <v>403</v>
       </c>
@@ -7869,7 +7869,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="203" ht="81" spans="1:6">
+    <row r="203" ht="84" spans="1:6">
       <c r="A203" t="s">
         <v>405</v>
       </c>
@@ -7886,7 +7886,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="204" ht="81" spans="1:6">
+    <row r="204" ht="84" spans="1:6">
       <c r="A204" t="s">
         <v>406</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="205" ht="121.5" spans="1:6">
+    <row r="205" ht="126" spans="1:6">
       <c r="A205" t="s">
         <v>407</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="206" ht="121.5" spans="1:6">
+    <row r="206" ht="126" spans="1:6">
       <c r="A206" t="s">
         <v>409</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="207" ht="121.5" spans="1:6">
+    <row r="207" ht="126" spans="1:6">
       <c r="A207" t="s">
         <v>411</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="208" ht="27" spans="1:6">
+    <row r="208" ht="42" spans="1:6">
       <c r="A208" t="s">
         <v>413</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="209" ht="121.5" spans="1:6">
+    <row r="209" ht="126" spans="1:6">
       <c r="A209" t="s">
         <v>415</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="210" ht="27" spans="1:6">
+    <row r="210" ht="42" spans="1:6">
       <c r="A210" t="s">
         <v>417</v>
       </c>
@@ -8005,7 +8005,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="211" ht="121.5" spans="1:6">
+    <row r="211" ht="126" spans="1:6">
       <c r="A211" t="s">
         <v>419</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="212" ht="121.5" spans="1:6">
+    <row r="212" ht="126" spans="1:6">
       <c r="A212" t="s">
         <v>421</v>
       </c>
@@ -8039,7 +8039,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="213" ht="121.5" spans="1:6">
+    <row r="213" ht="140" spans="1:6">
       <c r="A213" t="s">
         <v>423</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="214" ht="121.5" spans="1:6">
+    <row r="214" ht="126" spans="1:6">
       <c r="A214" t="s">
         <v>425</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="215" ht="54" spans="1:6">
+    <row r="215" ht="210" spans="1:6">
       <c r="A215" t="s">
         <v>427</v>
       </c>
@@ -8090,7 +8090,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="216" ht="81" spans="1:6">
+    <row r="216" ht="84" spans="1:6">
       <c r="A216" t="s">
         <v>429</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="217" ht="54" spans="1:6">
+    <row r="217" ht="168" spans="1:6">
       <c r="A217" t="s">
         <v>430</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="218" ht="27" spans="1:6">
+    <row r="218" ht="56" spans="1:6">
       <c r="A218" t="s">
         <v>431</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="219" ht="121.5" spans="1:6">
+    <row r="219" ht="126" spans="1:6">
       <c r="A219" t="s">
         <v>433</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="220" ht="108" spans="1:6">
+    <row r="220" ht="112" spans="1:6">
       <c r="A220" t="s">
         <v>435</v>
       </c>
@@ -8178,7 +8178,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="221" ht="54" spans="1:6">
+    <row r="221" ht="168" spans="1:6">
       <c r="A221" t="s">
         <v>438</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="222" ht="81" spans="1:6">
+    <row r="222" ht="84" spans="1:6">
       <c r="A222" t="s">
         <v>440</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="223" ht="81" spans="1:6">
+    <row r="223" ht="84" spans="1:6">
       <c r="A223" t="s">
         <v>442</v>
       </c>
@@ -8229,7 +8229,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="224" ht="121.5" spans="1:6">
+    <row r="224" ht="126" spans="1:6">
       <c r="A224" t="s">
         <v>444</v>
       </c>
@@ -8246,7 +8246,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="225" ht="40.5" spans="1:6">
+    <row r="225" ht="84" spans="1:6">
       <c r="A225" t="s">
         <v>446</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="226" ht="54" spans="1:6">
+    <row r="226" ht="182" spans="1:6">
       <c r="A226" t="s">
         <v>448</v>
       </c>
@@ -8280,7 +8280,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="227" ht="81" spans="1:6">
+    <row r="227" ht="84" spans="1:6">
       <c r="A227" t="s">
         <v>450</v>
       </c>
@@ -8297,7 +8297,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="228" ht="54" spans="1:6">
+    <row r="228" ht="210" spans="1:6">
       <c r="A228" t="s">
         <v>451</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="229" ht="27" spans="1:6">
+    <row r="229" ht="42" spans="1:6">
       <c r="A229" t="s">
         <v>453</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="230" ht="81" spans="1:6">
+    <row r="230" ht="84" spans="1:6">
       <c r="A230" t="s">
         <v>455</v>
       </c>
@@ -8348,7 +8348,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="231" ht="54" spans="1:6">
+    <row r="231" ht="182" spans="1:6">
       <c r="A231" t="s">
         <v>456</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="232" ht="27" spans="1:6">
+    <row r="232" ht="42" spans="1:6">
       <c r="A232" t="s">
         <v>457</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="233" ht="54" spans="1:6">
+    <row r="233" ht="196" spans="1:6">
       <c r="A233" t="s">
         <v>459</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="234" ht="27" spans="1:6">
+    <row r="234" ht="56" spans="1:6">
       <c r="A234" t="s">
         <v>461</v>
       </c>
@@ -8416,7 +8416,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="235" ht="54" spans="1:6">
+    <row r="235" ht="182" spans="1:6">
       <c r="A235" t="s">
         <v>463</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="236" ht="54" spans="1:6">
+    <row r="236" ht="168" spans="1:6">
       <c r="A236" t="s">
         <v>465</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="237" ht="54" spans="1:6">
+    <row r="237" ht="196" spans="1:6">
       <c r="A237" t="s">
         <v>467</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="238" ht="40.5" spans="1:6">
+    <row r="238" ht="154" spans="1:6">
       <c r="A238" t="s">
         <v>469</v>
       </c>
@@ -8484,7 +8484,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="239" ht="121.5" spans="1:6">
+    <row r="239" ht="126" spans="1:6">
       <c r="A239" t="s">
         <v>470</v>
       </c>
@@ -8501,7 +8501,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="240" ht="94.5" spans="1:6">
+    <row r="240" ht="98" spans="1:6">
       <c r="A240" t="s">
         <v>472</v>
       </c>
@@ -8518,7 +8518,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="241" ht="121.5" spans="1:6">
+    <row r="241" ht="126" spans="1:6">
       <c r="A241" t="s">
         <v>474</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="242" ht="121.5" spans="1:6">
+    <row r="242" ht="126" spans="1:6">
       <c r="A242" t="s">
         <v>476</v>
       </c>
@@ -8552,7 +8552,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="243" ht="54" spans="1:6">
+    <row r="243" ht="196" spans="1:6">
       <c r="A243" t="s">
         <v>478</v>
       </c>
@@ -8569,7 +8569,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="244" ht="108" spans="1:6">
+    <row r="244" ht="112" spans="1:6">
       <c r="A244" t="s">
         <v>480</v>
       </c>
@@ -8589,7 +8589,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="245" ht="81" spans="1:6">
+    <row r="245" ht="238" spans="1:6">
       <c r="A245" t="s">
         <v>483</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="246" ht="108" spans="1:6">
+    <row r="246" ht="112" spans="1:6">
       <c r="A246" t="s">
         <v>485</v>
       </c>
@@ -8626,7 +8626,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="247" ht="135" spans="1:6">
+    <row r="247" ht="140" spans="1:6">
       <c r="A247" t="s">
         <v>488</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="248" ht="54" spans="1:6">
+    <row r="248" ht="140" spans="1:6">
       <c r="A248" t="s">
         <v>490</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="249" ht="54" spans="1:6">
+    <row r="249" ht="126" spans="1:6">
       <c r="A249" t="s">
         <v>492</v>
       </c>
@@ -8677,7 +8677,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="250" ht="148.5" spans="1:6">
+    <row r="250" ht="154" spans="1:6">
       <c r="A250" t="s">
         <v>494</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="251" ht="108" spans="1:6">
+    <row r="251" ht="112" spans="1:6">
       <c r="A251" t="s">
         <v>496</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="252" ht="81" spans="1:6">
+    <row r="252" ht="84" spans="1:6">
       <c r="A252" t="s">
         <v>499</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="253" ht="121.5" spans="1:6">
+    <row r="253" ht="126" spans="1:6">
       <c r="A253" t="s">
         <v>501</v>
       </c>
@@ -8748,7 +8748,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="254" ht="27" spans="1:6">
+    <row r="254" ht="42" spans="1:6">
       <c r="A254" t="s">
         <v>503</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="255" ht="108" spans="1:6">
+    <row r="255" ht="112" spans="1:6">
       <c r="A255" t="s">
         <v>505</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="256" ht="54" spans="1:6">
+    <row r="256" ht="182" spans="1:6">
       <c r="A256" t="s">
         <v>507</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="257" ht="121.5" spans="1:6">
+    <row r="257" ht="126" spans="1:6">
       <c r="A257" t="s">
         <v>509</v>
       </c>
@@ -8816,7 +8816,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="258" ht="54" spans="1:6">
+    <row r="258" ht="182" spans="1:6">
       <c r="A258" t="s">
         <v>511</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="259" ht="81" spans="1:6">
+    <row r="259" ht="84" spans="1:6">
       <c r="A259" t="s">
         <v>513</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="260" ht="108" spans="1:6">
+    <row r="260" ht="112" spans="1:6">
       <c r="A260" t="s">
         <v>514</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="261" ht="81" spans="1:6">
+    <row r="261" ht="84" spans="1:6">
       <c r="A261" t="s">
         <v>517</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="262" ht="67.5" spans="1:6">
+    <row r="262" ht="224" spans="1:6">
       <c r="A262" t="s">
         <v>518</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="263" ht="54" spans="1:6">
+    <row r="263" ht="168" spans="1:6">
       <c r="A263" t="s">
         <v>520</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="264" ht="54" spans="1:6">
+    <row r="264" ht="196" spans="1:6">
       <c r="A264" t="s">
         <v>521</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="265" ht="67.5" spans="1:6">
+    <row r="265" ht="224" spans="1:6">
       <c r="A265" t="s">
         <v>523</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="266" ht="121.5" spans="1:6">
+    <row r="266" ht="126" spans="1:6">
       <c r="A266" t="s">
         <v>525</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="267" ht="108" spans="1:6">
+    <row r="267" ht="112" spans="1:6">
       <c r="A267" t="s">
         <v>528</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="268" ht="81" spans="1:6">
+    <row r="268" ht="266" spans="1:6">
       <c r="A268" t="s">
         <v>530</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="269" ht="108" spans="1:6">
+    <row r="269" ht="112" spans="1:6">
       <c r="A269" t="s">
         <v>532</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="270" ht="67.5" spans="1:6">
+    <row r="270" ht="196" spans="1:6">
       <c r="A270" t="s">
         <v>535</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="271" ht="54" spans="1:6">
+    <row r="271" ht="168" spans="1:6">
       <c r="A271" t="s">
         <v>537</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="272" ht="121.5" spans="1:6">
+    <row r="272" ht="126" spans="1:6">
       <c r="A272" t="s">
         <v>539</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="273" ht="81" spans="1:6">
+    <row r="273" ht="84" spans="1:6">
       <c r="A273" t="s">
         <v>541</v>
       </c>
@@ -9097,7 +9097,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="274" ht="121.5" spans="1:6">
+    <row r="274" ht="126" spans="1:6">
       <c r="A274" t="s">
         <v>542</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="275" ht="121.5" spans="1:6">
+    <row r="275" ht="126" spans="1:6">
       <c r="A275" t="s">
         <v>544</v>
       </c>
@@ -9131,7 +9131,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="276" ht="54" spans="1:6">
+    <row r="276" ht="196" spans="1:6">
       <c r="A276" t="s">
         <v>546</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="277" ht="135" spans="1:6">
+    <row r="277" ht="140" spans="1:6">
       <c r="A277" t="s">
         <v>548</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="278" ht="81" spans="1:6">
+    <row r="278" ht="84" spans="1:6">
       <c r="A278" t="s">
         <v>550</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="279" ht="121.5" spans="1:6">
+    <row r="279" ht="126" spans="1:6">
       <c r="A279" t="s">
         <v>551</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="280" ht="81" spans="1:6">
+    <row r="280" ht="84" spans="1:6">
       <c r="A280" t="s">
         <v>553</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="281" ht="67.5" spans="1:6">
+    <row r="281" ht="196" spans="1:6">
       <c r="A281" t="s">
         <v>554</v>
       </c>
@@ -9233,7 +9233,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="282" ht="27" spans="1:6">
+    <row r="282" ht="42" spans="1:6">
       <c r="A282" t="s">
         <v>556</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="283" ht="27" spans="1:6">
+    <row r="283" ht="28" spans="1:6">
       <c r="A283" t="s">
         <v>557</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="284" ht="27" spans="1:6">
+    <row r="284" ht="56" spans="1:6">
       <c r="A284" t="s">
         <v>558</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="285" ht="40.5" spans="1:6">
+    <row r="285" ht="70" spans="1:6">
       <c r="A285" t="s">
         <v>560</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="286" ht="27" spans="1:6">
+    <row r="286" ht="28" spans="1:6">
       <c r="A286" t="s">
         <v>562</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="287" ht="40.5" spans="1:6">
+    <row r="287" ht="70" spans="1:6">
       <c r="A287" t="s">
         <v>563</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="288" ht="27" spans="1:6">
+    <row r="288" ht="70" spans="1:6">
       <c r="A288" t="s">
         <v>565</v>
       </c>
@@ -9352,7 +9352,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="289" ht="135" spans="1:6">
+    <row r="289" ht="140" spans="1:6">
       <c r="A289" t="s">
         <v>567</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="290" ht="27" spans="1:6">
+    <row r="290" ht="56" spans="1:6">
       <c r="A290" t="s">
         <v>569</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="291" ht="27" spans="1:6">
+    <row r="291" ht="28" spans="1:6">
       <c r="A291" t="s">
         <v>571</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="292" ht="67.5" spans="1:6">
+    <row r="292" ht="210" spans="1:6">
       <c r="A292" t="s">
         <v>572</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="293" ht="40.5" spans="1:6">
+    <row r="293" ht="56" spans="1:6">
       <c r="A293" t="s">
         <v>574</v>
       </c>
@@ -9437,7 +9437,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="294" ht="67.5" spans="1:6">
+    <row r="294" ht="210" spans="1:6">
       <c r="A294" t="s">
         <v>576</v>
       </c>
@@ -9454,7 +9454,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="295" ht="81" spans="1:6">
+    <row r="295" ht="238" spans="1:6">
       <c r="A295" t="s">
         <v>578</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="296" ht="27" spans="1:6">
+    <row r="296" ht="42" spans="1:6">
       <c r="A296" t="s">
         <v>580</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="297" ht="108" spans="1:6">
+    <row r="297" ht="112" spans="1:6">
       <c r="A297" t="s">
         <v>582</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="298" ht="94.5" spans="1:6">
+    <row r="298" ht="98" spans="1:6">
       <c r="A298" t="s">
         <v>584</v>
       </c>
@@ -9525,7 +9525,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="299" ht="27" spans="1:6">
+    <row r="299" ht="56" spans="1:6">
       <c r="A299" t="s">
         <v>587</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="300" ht="40.5" spans="1:6">
+    <row r="300" ht="154" spans="1:6">
       <c r="A300" t="s">
         <v>589</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="301" ht="67.5" spans="1:6">
+    <row r="301" ht="252" spans="1:6">
       <c r="A301" t="s">
         <v>590</v>
       </c>
@@ -9576,7 +9576,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="302" ht="108" spans="1:6">
+    <row r="302" ht="112" spans="1:6">
       <c r="A302" t="s">
         <v>592</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="303" ht="94.5" spans="1:6">
+    <row r="303" ht="238" spans="1:6">
       <c r="A303" t="s">
         <v>594</v>
       </c>
@@ -9610,7 +9610,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="304" ht="108" spans="1:6">
+    <row r="304" ht="112" spans="1:6">
       <c r="A304" t="s">
         <v>596</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="305" ht="94.5" spans="1:6">
+    <row r="305" ht="98" spans="1:6">
       <c r="A305" t="s">
         <v>599</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="306" ht="108" spans="1:6">
+    <row r="306" ht="112" spans="1:6">
       <c r="A306" t="s">
         <v>602</v>
       </c>
@@ -9670,7 +9670,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="307" ht="108" spans="1:6">
+    <row r="307" ht="112" spans="1:6">
       <c r="A307" t="s">
         <v>605</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="308" ht="54" spans="1:6">
+    <row r="308" ht="196" spans="1:6">
       <c r="A308" t="s">
         <v>608</v>
       </c>
@@ -9707,7 +9707,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="309" ht="108" spans="1:6">
+    <row r="309" ht="112" spans="1:6">
       <c r="A309" t="s">
         <v>610</v>
       </c>
@@ -9727,7 +9727,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="310" ht="108" spans="1:6">
+    <row r="310" ht="112" spans="1:6">
       <c r="A310" t="s">
         <v>613</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="311" ht="202.5" spans="1:6">
+    <row r="311" ht="238" spans="1:6">
       <c r="A311" t="s">
         <v>616</v>
       </c>
@@ -9764,7 +9764,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="312" ht="54" spans="1:6">
+    <row r="312" ht="196" spans="1:6">
       <c r="A312" t="s">
         <v>618</v>
       </c>
@@ -9781,7 +9781,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="313" ht="121.5" spans="1:6">
+    <row r="313" ht="126" spans="1:6">
       <c r="A313" t="s">
         <v>620</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="314" ht="67.5" spans="1:6">
+    <row r="314" ht="210" spans="1:6">
       <c r="A314" t="s">
         <v>622</v>
       </c>
@@ -9815,7 +9815,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="315" ht="175.5" spans="1:6">
+    <row r="315" ht="182" spans="1:6">
       <c r="A315" t="s">
         <v>624</v>
       </c>
@@ -9835,7 +9835,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="316" ht="27" spans="1:6">
+    <row r="316" ht="28" spans="1:6">
       <c r="A316" t="s">
         <v>627</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="317" ht="27" spans="1:6">
+    <row r="317" ht="28" spans="1:6">
       <c r="A317" t="s">
         <v>629</v>
       </c>
@@ -9869,7 +9869,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="318" ht="81" spans="1:6">
+    <row r="318" ht="84" spans="1:6">
       <c r="A318" t="s">
         <v>631</v>
       </c>
@@ -9886,7 +9886,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="319" ht="67.5" spans="1:6">
+    <row r="319" ht="210" spans="1:6">
       <c r="A319" t="s">
         <v>633</v>
       </c>
@@ -9903,7 +9903,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="320" ht="40.5" spans="1:6">
+    <row r="320" ht="84" spans="1:6">
       <c r="A320" t="s">
         <v>635</v>
       </c>
@@ -9920,7 +9920,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="321" ht="81" spans="1:6">
+    <row r="321" ht="84" spans="1:6">
       <c r="A321" t="s">
         <v>637</v>
       </c>
@@ -9937,7 +9937,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="322" ht="54" spans="1:6">
+    <row r="322" ht="168" spans="1:6">
       <c r="A322" t="s">
         <v>639</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="323" ht="27" spans="1:6">
+    <row r="323" ht="56" spans="1:6">
       <c r="A323" t="s">
         <v>641</v>
       </c>
@@ -9971,7 +9971,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="324" ht="54" spans="1:6">
+    <row r="324" ht="182" spans="1:6">
       <c r="A324" t="s">
         <v>643</v>
       </c>
@@ -9988,7 +9988,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="325" ht="81" spans="1:6">
+    <row r="325" ht="84" spans="1:6">
       <c r="A325" t="s">
         <v>644</v>
       </c>
@@ -10005,7 +10005,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="326" ht="27" spans="1:6">
+    <row r="326" ht="42" spans="1:6">
       <c r="A326" t="s">
         <v>645</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="327" ht="54" spans="1:6">
+    <row r="327" ht="70" spans="1:6">
       <c r="A327" t="s">
         <v>647</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="328" ht="54" spans="1:6">
+    <row r="328" ht="196" spans="1:6">
       <c r="A328" t="s">
         <v>649</v>
       </c>
@@ -10059,7 +10059,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="329" ht="54" spans="1:6">
+    <row r="329" ht="70" spans="1:6">
       <c r="A329" t="s">
         <v>651</v>
       </c>
@@ -10079,7 +10079,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="330" ht="54" spans="1:6">
+    <row r="330" ht="182" spans="1:6">
       <c r="A330" t="s">
         <v>654</v>
       </c>
@@ -10096,7 +10096,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="331" ht="54" spans="1:6">
+    <row r="331" ht="182" spans="1:6">
       <c r="A331" t="s">
         <v>656</v>
       </c>
@@ -10113,7 +10113,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="332" ht="54" spans="1:6">
+    <row r="332" ht="168" spans="1:6">
       <c r="A332" t="s">
         <v>658</v>
       </c>
@@ -10130,7 +10130,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="333" ht="54" spans="1:6">
+    <row r="333" ht="182" spans="1:6">
       <c r="A333" t="s">
         <v>660</v>
       </c>
@@ -10147,7 +10147,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="334" ht="27" spans="1:6">
+    <row r="334" ht="56" spans="1:6">
       <c r="A334" t="s">
         <v>662</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="335" ht="54" spans="1:6">
+    <row r="335" ht="182" spans="1:6">
       <c r="A335" t="s">
         <v>664</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="336" ht="54" spans="1:6">
+    <row r="336" ht="182" spans="1:6">
       <c r="A336" t="s">
         <v>666</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="337" ht="81" spans="1:6">
+    <row r="337" ht="84" spans="1:6">
       <c r="A337" t="s">
         <v>668</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="338" ht="27" spans="1:6">
+    <row r="338" ht="42" spans="1:6">
       <c r="A338" t="s">
         <v>669</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="339" ht="27" spans="1:6">
+    <row r="339" ht="42" spans="1:6">
       <c r="A339" t="s">
         <v>671</v>
       </c>
@@ -10249,7 +10249,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="340" ht="54" spans="1:6">
+    <row r="340" ht="182" spans="1:6">
       <c r="A340" t="s">
         <v>672</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="341" ht="54" spans="1:6">
+    <row r="341" ht="168" spans="1:6">
       <c r="A341" t="s">
         <v>674</v>
       </c>
@@ -10283,7 +10283,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="342" ht="67.5" spans="1:6">
+    <row r="342" ht="224" spans="1:6">
       <c r="A342" t="s">
         <v>676</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="343" ht="108" spans="1:6">
+    <row r="343" ht="112" spans="1:6">
       <c r="A343" t="s">
         <v>678</v>
       </c>
@@ -10317,7 +10317,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="344" ht="94.5" spans="1:6">
+    <row r="344" ht="112" spans="1:6">
       <c r="A344" t="s">
         <v>680</v>
       </c>
@@ -10337,7 +10337,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="345" ht="54" spans="1:6">
+    <row r="345" ht="182" spans="1:6">
       <c r="A345" t="s">
         <v>683</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="346" ht="54" spans="1:6">
+    <row r="346" ht="196" spans="1:6">
       <c r="A346" t="s">
         <v>685</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="347" ht="40.5" spans="1:6">
+    <row r="347" ht="84" spans="1:6">
       <c r="A347" t="s">
         <v>687</v>
       </c>
@@ -10388,7 +10388,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="348" ht="81" spans="1:6">
+    <row r="348" ht="224" spans="1:6">
       <c r="A348" t="s">
         <v>689</v>
       </c>
@@ -10405,7 +10405,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="349" ht="54" spans="1:6">
+    <row r="349" ht="182" spans="1:6">
       <c r="A349" t="s">
         <v>691</v>
       </c>
@@ -10422,7 +10422,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="350" ht="108" spans="1:6">
+    <row r="350" ht="112" spans="1:6">
       <c r="A350" t="s">
         <v>693</v>
       </c>
@@ -10439,7 +10439,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="351" ht="81" spans="1:6">
+    <row r="351" ht="84" spans="1:6">
       <c r="A351" t="s">
         <v>695</v>
       </c>
@@ -10456,7 +10456,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="352" ht="81" spans="1:6">
+    <row r="352" ht="84" spans="1:6">
       <c r="A352" t="s">
         <v>697</v>
       </c>
@@ -10473,7 +10473,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="353" ht="135" spans="1:6">
+    <row r="353" ht="140" spans="1:6">
       <c r="A353" t="s">
         <v>699</v>
       </c>

--- a/Step4-RunTestCase/final-data/cross_categorized_results.xlsx
+++ b/Step4-RunTestCase/final-data/cross_categorized_results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="cross_categorized_results" sheetId="1" r:id="rId1"/>
@@ -4372,13 +4372,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F353"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="48.3727272727273" customWidth="1"/>
-    <col min="3" max="3" width="33.2545454545455" customWidth="1"/>
-    <col min="4" max="4" width="65.7545454545455" customWidth="1"/>
-    <col min="5" max="5" width="36.1272727272727" customWidth="1"/>
-    <col min="6" max="6" width="98.6272727272727" customWidth="1"/>
+    <col min="1" max="1" width="48.375" customWidth="1"/>
+    <col min="3" max="3" width="33.25" customWidth="1"/>
+    <col min="4" max="4" width="65.75" customWidth="1"/>
+    <col min="5" max="5" width="36.125" customWidth="1"/>
+    <col min="6" max="6" width="98.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4401,7 +4401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="168" spans="1:6">
+    <row r="2" ht="54" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="112" spans="1:6">
+    <row r="3" ht="108" spans="1:6">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="112" spans="1:6">
+    <row r="4" ht="108" spans="1:6">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" ht="224" spans="1:6">
+    <row r="5" ht="67.5" spans="1:6">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" ht="168" spans="1:6">
+    <row r="6" ht="40.5" spans="1:6">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" ht="182" spans="1:6">
+    <row r="7" ht="54" spans="1:6">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" ht="42" spans="1:6">
+    <row r="8" ht="40.5" spans="1:6">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" ht="98" spans="1:6">
+    <row r="9" ht="94.5" spans="1:6">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" ht="112" spans="1:6">
+    <row r="10" ht="108" spans="1:6">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="112" spans="1:6">
+    <row r="11" ht="108" spans="1:6">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" ht="126" spans="1:6">
+    <row r="12" ht="121.5" spans="1:6">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" ht="84" spans="1:6">
+    <row r="13" ht="81" spans="1:6">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" ht="56" spans="1:6">
+    <row r="14" ht="27" spans="1:6">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" ht="42" spans="1:6">
+    <row r="15" ht="27" spans="1:6">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" ht="126" spans="1:6">
+    <row r="16" ht="121.5" spans="1:6">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" ht="210" spans="1:6">
+    <row r="17" ht="54" spans="1:6">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" ht="42" spans="1:6">
+    <row r="18" ht="27" spans="1:6">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" ht="84" spans="1:6">
+    <row r="19" ht="81" spans="1:6">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" ht="140" spans="1:6">
+    <row r="20" ht="135" spans="1:6">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" ht="182" spans="1:6">
+    <row r="21" ht="54" spans="1:6">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" ht="182" spans="1:6">
+    <row r="22" ht="54" spans="1:6">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" ht="182" spans="1:6">
+    <row r="23" ht="54" spans="1:6">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" ht="126" spans="1:6">
+    <row r="24" ht="121.5" spans="1:6">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" ht="210" spans="1:6">
+    <row r="25" ht="54" spans="1:6">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" ht="182" spans="1:6">
+    <row r="26" ht="54" spans="1:6">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" ht="112" spans="1:6">
+    <row r="28" ht="108" spans="1:6">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" ht="126" spans="1:6">
+    <row r="29" ht="121.5" spans="1:6">
       <c r="A29" t="s">
         <v>71</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" ht="154" spans="1:6">
+    <row r="30" ht="148.5" spans="1:6">
       <c r="A30" t="s">
         <v>73</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" ht="154" spans="1:6">
+    <row r="31" ht="148.5" spans="1:6">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" ht="28" spans="1:6">
+    <row r="32" ht="27" spans="1:6">
       <c r="A32" t="s">
         <v>77</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" ht="56" spans="1:6">
+    <row r="33" ht="27" spans="1:6">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -4957,7 +4957,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" ht="154" spans="1:6">
+    <row r="34" ht="148.5" spans="1:6">
       <c r="A34" t="s">
         <v>81</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" ht="154" spans="1:6">
+    <row r="35" ht="148.5" spans="1:6">
       <c r="A35" t="s">
         <v>83</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="36" ht="126" spans="1:6">
+    <row r="36" ht="121.5" spans="1:6">
       <c r="A36" t="s">
         <v>86</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" ht="42" spans="1:6">
+    <row r="37" ht="40.5" spans="1:6">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" ht="182" spans="1:6">
+    <row r="38" ht="54" spans="1:6">
       <c r="A38" t="s">
         <v>90</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" ht="182" spans="1:6">
+    <row r="39" ht="54" spans="1:6">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" ht="70" spans="1:6">
+    <row r="40" ht="40.5" spans="1:6">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" ht="84" spans="1:6">
+    <row r="41" ht="81" spans="1:6">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" ht="28" spans="1:6">
+    <row r="42" ht="27" spans="1:6">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" ht="126" spans="1:6">
+    <row r="43" ht="121.5" spans="1:6">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" ht="84" spans="1:6">
+    <row r="44" ht="81" spans="1:6">
       <c r="A44" t="s">
         <v>100</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" ht="126" spans="1:6">
+    <row r="45" ht="121.5" spans="1:6">
       <c r="A45" t="s">
         <v>101</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" ht="28" spans="1:6">
+    <row r="47" ht="27" spans="1:6">
       <c r="A47" t="s">
         <v>104</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" ht="84" spans="1:6">
+    <row r="48" ht="81" spans="1:6">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" ht="182" spans="1:6">
+    <row r="49" ht="54" spans="1:6">
       <c r="A49" t="s">
         <v>106</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="50" ht="56" spans="1:6">
+    <row r="50" ht="27" spans="1:6">
       <c r="A50" t="s">
         <v>108</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="51" ht="70" spans="1:6">
+    <row r="51" ht="27" spans="1:6">
       <c r="A51" t="s">
         <v>110</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" ht="42" spans="1:6">
+    <row r="52" ht="27" spans="1:6">
       <c r="A52" t="s">
         <v>112</v>
       </c>
@@ -5277,7 +5277,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="53" ht="70" spans="1:6">
+    <row r="53" ht="27" spans="1:6">
       <c r="A53" t="s">
         <v>114</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="54" ht="140" spans="1:6">
+    <row r="54" ht="135" spans="1:6">
       <c r="A54" t="s">
         <v>116</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="55" ht="84" spans="1:6">
+    <row r="55" ht="81" spans="1:6">
       <c r="A55" t="s">
         <v>118</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" ht="84" spans="1:6">
+    <row r="56" ht="81" spans="1:6">
       <c r="A56" t="s">
         <v>119</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" ht="140" spans="1:6">
+    <row r="57" ht="135" spans="1:6">
       <c r="A57" t="s">
         <v>120</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="58" ht="224" spans="1:6">
+    <row r="58" ht="67.5" spans="1:6">
       <c r="A58" t="s">
         <v>122</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="59" ht="84" spans="1:6">
+    <row r="59" ht="81" spans="1:6">
       <c r="A59" t="s">
         <v>124</v>
       </c>
@@ -5396,7 +5396,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="60" ht="84" spans="1:6">
+    <row r="60" ht="81" spans="1:6">
       <c r="A60" t="s">
         <v>125</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" ht="140" spans="1:6">
+    <row r="61" ht="135" spans="1:6">
       <c r="A61" t="s">
         <v>126</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="62" ht="140" spans="1:6">
+    <row r="62" ht="135" spans="1:6">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="63" ht="84" spans="1:6">
+    <row r="63" ht="81" spans="1:6">
       <c r="A63" t="s">
         <v>130</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" ht="182" spans="1:6">
+    <row r="64" ht="54" spans="1:6">
       <c r="A64" t="s">
         <v>131</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="65" ht="140" spans="1:6">
+    <row r="65" ht="135" spans="1:6">
       <c r="A65" t="s">
         <v>133</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="66" ht="126" spans="1:6">
+    <row r="66" ht="121.5" spans="1:6">
       <c r="A66" t="s">
         <v>135</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="67" ht="140" spans="1:6">
+    <row r="67" ht="135" spans="1:6">
       <c r="A67" t="s">
         <v>138</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="68" ht="140" spans="1:6">
+    <row r="68" ht="135" spans="1:6">
       <c r="A68" t="s">
         <v>140</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="69" ht="84" spans="1:6">
+    <row r="69" ht="81" spans="1:6">
       <c r="A69" t="s">
         <v>142</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="70" ht="56" spans="1:6">
+    <row r="70" ht="27" spans="1:6">
       <c r="A70" t="s">
         <v>144</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="71" ht="168" spans="1:6">
+    <row r="71" ht="54" spans="1:6">
       <c r="A71" t="s">
         <v>146</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="72" ht="112" spans="1:6">
+    <row r="72" ht="108" spans="1:6">
       <c r="A72" t="s">
         <v>148</v>
       </c>
@@ -5620,7 +5620,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="73" ht="84" spans="1:6">
+    <row r="73" ht="40.5" spans="1:6">
       <c r="A73" t="s">
         <v>150</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" ht="56" spans="1:6">
+    <row r="75" ht="27" spans="1:6">
       <c r="A75" t="s">
         <v>153</v>
       </c>
@@ -5682,7 +5682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" ht="84" spans="1:6">
+    <row r="77" ht="81" spans="1:6">
       <c r="A77" t="s">
         <v>156</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" ht="28" spans="1:6">
+    <row r="78" ht="27" spans="1:6">
       <c r="A78" t="s">
         <v>158</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="80" ht="112" spans="1:6">
+    <row r="80" ht="108" spans="1:6">
       <c r="A80" t="s">
         <v>162</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="81" ht="112" spans="1:6">
+    <row r="81" ht="108" spans="1:6">
       <c r="A81" t="s">
         <v>164</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="82" ht="112" spans="1:6">
+    <row r="82" ht="108" spans="1:6">
       <c r="A82" t="s">
         <v>168</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="83" ht="112" spans="1:6">
+    <row r="83" ht="108" spans="1:6">
       <c r="A83" t="s">
         <v>170</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" ht="42" spans="1:6">
+    <row r="85" ht="27" spans="1:6">
       <c r="A85" t="s">
         <v>174</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="86" ht="112" spans="1:6">
+    <row r="86" ht="108" spans="1:6">
       <c r="A86" t="s">
         <v>176</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="87" ht="84" spans="1:6">
+    <row r="87" ht="81" spans="1:6">
       <c r="A87" t="s">
         <v>178</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" ht="84" spans="1:6">
+    <row r="88" ht="81" spans="1:6">
       <c r="A88" t="s">
         <v>179</v>
       </c>
@@ -5895,7 +5895,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="89" ht="84" spans="1:6">
+    <row r="89" ht="81" spans="1:6">
       <c r="A89" t="s">
         <v>180</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="90" ht="84" spans="1:6">
+    <row r="90" ht="81" spans="1:6">
       <c r="A90" t="s">
         <v>181</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="91" ht="84" spans="1:6">
+    <row r="91" ht="81" spans="1:6">
       <c r="A91" t="s">
         <v>182</v>
       </c>
@@ -5946,7 +5946,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" ht="84" spans="1:6">
+    <row r="92" ht="81" spans="1:6">
       <c r="A92" t="s">
         <v>183</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" ht="84" spans="1:6">
+    <row r="94" ht="81" spans="1:6">
       <c r="A94" t="s">
         <v>185</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="95" ht="84" spans="1:6">
+    <row r="95" ht="81" spans="1:6">
       <c r="A95" t="s">
         <v>186</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="96" ht="84" spans="1:6">
+    <row r="96" ht="81" spans="1:6">
       <c r="A96" t="s">
         <v>188</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="97" ht="168" spans="1:6">
+    <row r="97" ht="54" spans="1:6">
       <c r="A97" t="s">
         <v>189</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="98" ht="126" spans="1:6">
+    <row r="98" ht="121.5" spans="1:6">
       <c r="A98" t="s">
         <v>191</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="99" ht="182" spans="1:6">
+    <row r="99" ht="54" spans="1:6">
       <c r="A99" t="s">
         <v>193</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="100" ht="112" spans="1:6">
+    <row r="100" ht="108" spans="1:6">
       <c r="A100" t="s">
         <v>195</v>
       </c>
@@ -6096,7 +6096,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="101" ht="210" spans="1:6">
+    <row r="101" ht="67.5" spans="1:6">
       <c r="A101" t="s">
         <v>197</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="102" ht="112" spans="1:6">
+    <row r="102" ht="108" spans="1:6">
       <c r="A102" t="s">
         <v>199</v>
       </c>
@@ -6133,7 +6133,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="103" ht="182" spans="1:6">
+    <row r="103" ht="54" spans="1:6">
       <c r="A103" t="s">
         <v>202</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="104" ht="210" spans="1:6">
+    <row r="104" ht="54" spans="1:6">
       <c r="A104" t="s">
         <v>204</v>
       </c>
@@ -6167,7 +6167,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="105" ht="112" spans="1:6">
+    <row r="105" ht="108" spans="1:6">
       <c r="A105" t="s">
         <v>206</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="106" ht="112" spans="1:6">
+    <row r="106" ht="108" spans="1:6">
       <c r="A106" t="s">
         <v>208</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="107" ht="126" spans="1:6">
+    <row r="107" ht="121.5" spans="1:6">
       <c r="A107" t="s">
         <v>210</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="108" ht="154" spans="1:6">
+    <row r="108" ht="40.5" spans="1:6">
       <c r="A108" t="s">
         <v>212</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="109" ht="126" spans="1:6">
+    <row r="109" ht="121.5" spans="1:6">
       <c r="A109" t="s">
         <v>214</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="110" ht="182" spans="1:6">
+    <row r="110" ht="54" spans="1:6">
       <c r="A110" t="s">
         <v>216</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="111" ht="182" spans="1:6">
+    <row r="111" ht="54" spans="1:6">
       <c r="A111" t="s">
         <v>218</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="112" ht="168" spans="1:6">
+    <row r="112" ht="54" spans="1:6">
       <c r="A112" t="s">
         <v>220</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" ht="112" spans="1:6">
+    <row r="113" ht="108" spans="1:6">
       <c r="A113" t="s">
         <v>221</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="114" ht="280" spans="1:6">
+    <row r="114" ht="121.5" spans="1:6">
       <c r="A114" t="s">
         <v>223</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="115" ht="182" spans="1:6">
+    <row r="115" ht="54" spans="1:6">
       <c r="A115" t="s">
         <v>226</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="116" ht="84" spans="1:6">
+    <row r="116" ht="81" spans="1:6">
       <c r="A116" t="s">
         <v>228</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="117" ht="126" spans="1:6">
+    <row r="117" ht="121.5" spans="1:6">
       <c r="A117" t="s">
         <v>230</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="118" ht="98" spans="1:6">
+    <row r="118" ht="94.5" spans="1:6">
       <c r="A118" t="s">
         <v>232</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="119" ht="196" spans="1:6">
+    <row r="119" ht="54" spans="1:6">
       <c r="A119" t="s">
         <v>235</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="120" ht="196" spans="1:6">
+    <row r="120" ht="54" spans="1:6">
       <c r="A120" t="s">
         <v>237</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="121" ht="196" spans="1:6">
+    <row r="121" ht="54" spans="1:6">
       <c r="A121" t="s">
         <v>239</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="122" ht="182" spans="1:6">
+    <row r="122" ht="54" spans="1:6">
       <c r="A122" t="s">
         <v>241</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="123" ht="112" spans="1:6">
+    <row r="123" ht="108" spans="1:6">
       <c r="A123" t="s">
         <v>243</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="124" ht="112" spans="1:6">
+    <row r="124" ht="108" spans="1:6">
       <c r="A124" t="s">
         <v>245</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="125" ht="168" spans="1:6">
+    <row r="125" ht="54" spans="1:6">
       <c r="A125" t="s">
         <v>247</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="126" ht="112" spans="1:6">
+    <row r="126" ht="108" spans="1:6">
       <c r="A126" t="s">
         <v>249</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="127" ht="168" spans="1:6">
+    <row r="127" ht="54" spans="1:6">
       <c r="A127" t="s">
         <v>251</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="128" ht="126" spans="1:6">
+    <row r="128" ht="94.5" spans="1:6">
       <c r="A128" t="s">
         <v>252</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="129" ht="84" spans="1:6">
+    <row r="129" ht="81" spans="1:6">
       <c r="A129" t="s">
         <v>254</v>
       </c>
@@ -6595,7 +6595,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" ht="182" spans="1:6">
+    <row r="130" ht="54" spans="1:6">
       <c r="A130" t="s">
         <v>255</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="131" ht="182" spans="1:6">
+    <row r="131" ht="54" spans="1:6">
       <c r="A131" t="s">
         <v>257</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="132" ht="168" spans="1:6">
+    <row r="132" ht="54" spans="1:6">
       <c r="A132" t="s">
         <v>259</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" ht="98" spans="1:6">
+    <row r="133" ht="94.5" spans="1:6">
       <c r="A133" t="s">
         <v>260</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="134" ht="112" spans="1:6">
+    <row r="134" ht="108" spans="1:6">
       <c r="A134" t="s">
         <v>263</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="135" ht="168" spans="1:6">
+    <row r="135" ht="54" spans="1:6">
       <c r="A135" t="s">
         <v>266</v>
       </c>
@@ -6703,7 +6703,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="136" ht="154" spans="1:6">
+    <row r="136" ht="94.5" spans="1:6">
       <c r="A136" t="s">
         <v>268</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="137" ht="112" spans="1:6">
+    <row r="137" ht="94.5" spans="1:6">
       <c r="A137" t="s">
         <v>271</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="138" ht="406" spans="1:6">
+    <row r="138" ht="378" spans="1:6">
       <c r="A138" t="s">
         <v>273</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" ht="84" spans="1:6">
+    <row r="139" ht="81" spans="1:6">
       <c r="A139" t="s">
         <v>276</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="140" ht="112" spans="1:6">
+    <row r="140" ht="108" spans="1:6">
       <c r="A140" t="s">
         <v>278</v>
       </c>
@@ -6797,7 +6797,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="141" ht="112" spans="1:6">
+    <row r="141" ht="108" spans="1:6">
       <c r="A141" t="s">
         <v>280</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" ht="112" spans="1:6">
+    <row r="142" ht="108" spans="1:6">
       <c r="A142" t="s">
         <v>282</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="143" ht="112" spans="1:6">
+    <row r="143" ht="108" spans="1:6">
       <c r="A143" t="s">
         <v>285</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="144" ht="112" spans="1:6">
+    <row r="144" ht="108" spans="1:6">
       <c r="A144" t="s">
         <v>287</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="145" ht="112" spans="1:6">
+    <row r="145" ht="108" spans="1:6">
       <c r="A145" t="s">
         <v>289</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="146" ht="126" spans="1:6">
+    <row r="146" ht="121.5" spans="1:6">
       <c r="A146" t="s">
         <v>292</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="147" ht="84" spans="1:6">
+    <row r="147" ht="40.5" spans="1:6">
       <c r="A147" t="s">
         <v>294</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="148" ht="196" spans="1:6">
+    <row r="148" ht="54" spans="1:6">
       <c r="A148" t="s">
         <v>296</v>
       </c>
@@ -6939,7 +6939,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="149" ht="98" spans="1:6">
+    <row r="149" ht="40.5" spans="1:6">
       <c r="A149" t="s">
         <v>298</v>
       </c>
@@ -6956,7 +6956,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="150" ht="84" spans="1:6">
+    <row r="150" ht="40.5" spans="1:6">
       <c r="A150" t="s">
         <v>300</v>
       </c>
@@ -6973,7 +6973,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="151" ht="196" spans="1:6">
+    <row r="151" ht="54" spans="1:6">
       <c r="A151" t="s">
         <v>302</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="152" ht="154" spans="1:6">
+    <row r="152" ht="40.5" spans="1:6">
       <c r="A152" t="s">
         <v>304</v>
       </c>
@@ -7007,7 +7007,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="153" ht="140" spans="1:6">
+    <row r="153" ht="135" spans="1:6">
       <c r="A153" t="s">
         <v>306</v>
       </c>
@@ -7027,7 +7027,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="154" ht="182" spans="1:6">
+    <row r="154" ht="54" spans="1:6">
       <c r="A154" t="s">
         <v>309</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="155" ht="112" spans="1:6">
+    <row r="155" ht="108" spans="1:6">
       <c r="A155" t="s">
         <v>311</v>
       </c>
@@ -7061,7 +7061,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="156" ht="168" spans="1:6">
+    <row r="156" ht="54" spans="1:6">
       <c r="A156" t="s">
         <v>313</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="157" ht="42" spans="1:6">
+    <row r="157" ht="27" spans="1:6">
       <c r="A157" t="s">
         <v>315</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="158" ht="56" spans="1:6">
+    <row r="158" ht="27" spans="1:6">
       <c r="A158" t="s">
         <v>317</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="159" ht="56" spans="1:6">
+    <row r="159" ht="27" spans="1:6">
       <c r="A159" t="s">
         <v>319</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="160" ht="56" spans="1:6">
+    <row r="160" ht="27" spans="1:6">
       <c r="A160" t="s">
         <v>321</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="161" ht="42" spans="1:6">
+    <row r="161" ht="27" spans="1:6">
       <c r="A161" t="s">
         <v>323</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="162" ht="42" spans="1:6">
+    <row r="162" ht="27" spans="1:6">
       <c r="A162" t="s">
         <v>325</v>
       </c>
@@ -7180,7 +7180,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="163" ht="56" spans="1:6">
+    <row r="163" ht="27" spans="1:6">
       <c r="A163" t="s">
         <v>327</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="164" ht="56" spans="1:6">
+    <row r="164" ht="27" spans="1:6">
       <c r="A164" t="s">
         <v>329</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="165" ht="84" spans="1:6">
+    <row r="165" ht="81" spans="1:6">
       <c r="A165" t="s">
         <v>330</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="166" ht="42" spans="1:6">
+    <row r="166" ht="27" spans="1:6">
       <c r="A166" t="s">
         <v>331</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" ht="224" spans="1:6">
+    <row r="167" ht="67.5" spans="1:6">
       <c r="A167" t="s">
         <v>333</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="168" ht="168" spans="1:6">
+    <row r="168" ht="54" spans="1:6">
       <c r="A168" t="s">
         <v>335</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" ht="196" spans="1:6">
+    <row r="169" ht="54" spans="1:6">
       <c r="A169" t="s">
         <v>336</v>
       </c>
@@ -7299,7 +7299,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="170" ht="168" spans="1:6">
+    <row r="170" ht="54" spans="1:6">
       <c r="A170" t="s">
         <v>338</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="171" ht="182" spans="1:6">
+    <row r="171" ht="54" spans="1:6">
       <c r="A171" t="s">
         <v>340</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="172" ht="112" spans="1:6">
+    <row r="172" ht="108" spans="1:6">
       <c r="A172" t="s">
         <v>342</v>
       </c>
@@ -7350,7 +7350,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="173" ht="182" spans="1:6">
+    <row r="173" ht="54" spans="1:6">
       <c r="A173" t="s">
         <v>344</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="174" ht="112" spans="1:6">
+    <row r="174" ht="108" spans="1:6">
       <c r="A174" t="s">
         <v>346</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" ht="112" spans="1:6">
+    <row r="175" ht="108" spans="1:6">
       <c r="A175" t="s">
         <v>348</v>
       </c>
@@ -7401,7 +7401,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="176" ht="196" spans="1:6">
+    <row r="176" ht="54" spans="1:6">
       <c r="A176" t="s">
         <v>350</v>
       </c>
@@ -7418,7 +7418,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="177" ht="196" spans="1:6">
+    <row r="177" ht="54" spans="1:6">
       <c r="A177" t="s">
         <v>352</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178" ht="182" spans="1:6">
+    <row r="178" ht="54" spans="1:6">
       <c r="A178" t="s">
         <v>354</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="179" ht="266" spans="1:6">
+    <row r="179" ht="108" spans="1:6">
       <c r="A179" t="s">
         <v>356</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" ht="56" spans="1:6">
+    <row r="180" ht="27" spans="1:6">
       <c r="A180" t="s">
         <v>359</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="181" ht="112" spans="1:6">
+    <row r="181" ht="108" spans="1:6">
       <c r="A181" t="s">
         <v>361</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="182" ht="70" spans="1:6">
+    <row r="182" ht="40.5" spans="1:6">
       <c r="A182" t="s">
         <v>364</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="183" ht="70" spans="1:6">
+    <row r="183" ht="27" spans="1:6">
       <c r="A183" t="s">
         <v>366</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="184" ht="182" spans="1:6">
+    <row r="184" ht="54" spans="1:6">
       <c r="A184" t="s">
         <v>368</v>
       </c>
@@ -7560,7 +7560,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="185" ht="182" spans="1:6">
+    <row r="185" ht="54" spans="1:6">
       <c r="A185" t="s">
         <v>370</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="186" ht="112" spans="1:6">
+    <row r="186" ht="108" spans="1:6">
       <c r="A186" t="s">
         <v>372</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="187" ht="56" spans="1:6">
+    <row r="187" ht="40.5" spans="1:6">
       <c r="A187" t="s">
         <v>374</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="188" ht="42" spans="1:6">
+    <row r="188" ht="27" spans="1:6">
       <c r="A188" t="s">
         <v>376</v>
       </c>
@@ -7628,7 +7628,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="189" ht="182" spans="1:6">
+    <row r="189" ht="54" spans="1:6">
       <c r="A189" t="s">
         <v>378</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="190" ht="196" spans="1:6">
+    <row r="190" ht="54" spans="1:6">
       <c r="A190" t="s">
         <v>380</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="191" ht="70" spans="1:6">
+    <row r="191" ht="40.5" spans="1:6">
       <c r="A191" t="s">
         <v>382</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="192" ht="154" spans="1:6">
+    <row r="192" ht="67.5" spans="1:6">
       <c r="A192" t="s">
         <v>384</v>
       </c>
@@ -7696,7 +7696,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="193" ht="154" spans="1:6">
+    <row r="193" ht="40.5" spans="1:6">
       <c r="A193" t="s">
         <v>386</v>
       </c>
@@ -7713,7 +7713,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="194" ht="70" spans="1:6">
+    <row r="194" ht="54" spans="1:6">
       <c r="A194" t="s">
         <v>388</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="195" ht="56" spans="1:6">
+    <row r="195" ht="27" spans="1:6">
       <c r="A195" t="s">
         <v>391</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="196" ht="84" spans="1:6">
+    <row r="196" ht="81" spans="1:6">
       <c r="A196" t="s">
         <v>393</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="197" ht="154" spans="1:6">
+    <row r="197" ht="40.5" spans="1:6">
       <c r="A197" t="s">
         <v>394</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="198" ht="42" spans="1:6">
+    <row r="198" ht="27" spans="1:6">
       <c r="A198" t="s">
         <v>396</v>
       </c>
@@ -7801,7 +7801,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="199" ht="84" spans="1:6">
+    <row r="199" ht="81" spans="1:6">
       <c r="A199" t="s">
         <v>398</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200" ht="70" spans="1:6">
+    <row r="200" ht="40.5" spans="1:6">
       <c r="A200" t="s">
         <v>399</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="201" ht="182" spans="1:6">
+    <row r="201" ht="54" spans="1:6">
       <c r="A201" t="s">
         <v>401</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="202" ht="42" spans="1:6">
+    <row r="202" ht="27" spans="1:6">
       <c r="A202" t="s">
         <v>403</v>
       </c>
@@ -7869,7 +7869,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="203" ht="84" spans="1:6">
+    <row r="203" ht="81" spans="1:6">
       <c r="A203" t="s">
         <v>405</v>
       </c>
@@ -7886,7 +7886,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="204" ht="84" spans="1:6">
+    <row r="204" ht="81" spans="1:6">
       <c r="A204" t="s">
         <v>406</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="205" ht="126" spans="1:6">
+    <row r="205" ht="121.5" spans="1:6">
       <c r="A205" t="s">
         <v>407</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="206" ht="126" spans="1:6">
+    <row r="206" ht="121.5" spans="1:6">
       <c r="A206" t="s">
         <v>409</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="207" ht="126" spans="1:6">
+    <row r="207" ht="121.5" spans="1:6">
       <c r="A207" t="s">
         <v>411</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="208" ht="42" spans="1:6">
+    <row r="208" ht="27" spans="1:6">
       <c r="A208" t="s">
         <v>413</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="209" ht="126" spans="1:6">
+    <row r="209" ht="121.5" spans="1:6">
       <c r="A209" t="s">
         <v>415</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="210" ht="42" spans="1:6">
+    <row r="210" ht="27" spans="1:6">
       <c r="A210" t="s">
         <v>417</v>
       </c>
@@ -8005,7 +8005,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="211" ht="126" spans="1:6">
+    <row r="211" ht="121.5" spans="1:6">
       <c r="A211" t="s">
         <v>419</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="212" ht="126" spans="1:6">
+    <row r="212" ht="121.5" spans="1:6">
       <c r="A212" t="s">
         <v>421</v>
       </c>
@@ -8039,7 +8039,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="213" ht="140" spans="1:6">
+    <row r="213" ht="121.5" spans="1:6">
       <c r="A213" t="s">
         <v>423</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="214" ht="126" spans="1:6">
+    <row r="214" ht="121.5" spans="1:6">
       <c r="A214" t="s">
         <v>425</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="215" ht="210" spans="1:6">
+    <row r="215" ht="54" spans="1:6">
       <c r="A215" t="s">
         <v>427</v>
       </c>
@@ -8090,7 +8090,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="216" ht="84" spans="1:6">
+    <row r="216" ht="81" spans="1:6">
       <c r="A216" t="s">
         <v>429</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="217" ht="168" spans="1:6">
+    <row r="217" ht="54" spans="1:6">
       <c r="A217" t="s">
         <v>430</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="218" ht="56" spans="1:6">
+    <row r="218" ht="27" spans="1:6">
       <c r="A218" t="s">
         <v>431</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="219" ht="126" spans="1:6">
+    <row r="219" ht="121.5" spans="1:6">
       <c r="A219" t="s">
         <v>433</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="220" ht="112" spans="1:6">
+    <row r="220" ht="108" spans="1:6">
       <c r="A220" t="s">
         <v>435</v>
       </c>
@@ -8178,7 +8178,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="221" ht="168" spans="1:6">
+    <row r="221" ht="54" spans="1:6">
       <c r="A221" t="s">
         <v>438</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="222" ht="84" spans="1:6">
+    <row r="222" ht="81" spans="1:6">
       <c r="A222" t="s">
         <v>440</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="223" ht="84" spans="1:6">
+    <row r="223" ht="81" spans="1:6">
       <c r="A223" t="s">
         <v>442</v>
       </c>
@@ -8229,7 +8229,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="224" ht="126" spans="1:6">
+    <row r="224" ht="121.5" spans="1:6">
       <c r="A224" t="s">
         <v>444</v>
       </c>
@@ -8246,7 +8246,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="225" ht="84" spans="1:6">
+    <row r="225" ht="40.5" spans="1:6">
       <c r="A225" t="s">
         <v>446</v>
       </c>
@@ -8263,7 +8263,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="226" ht="182" spans="1:6">
+    <row r="226" ht="54" spans="1:6">
       <c r="A226" t="s">
         <v>448</v>
       </c>
@@ -8280,7 +8280,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="227" ht="84" spans="1:6">
+    <row r="227" ht="81" spans="1:6">
       <c r="A227" t="s">
         <v>450</v>
       </c>
@@ -8297,7 +8297,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="228" ht="210" spans="1:6">
+    <row r="228" ht="54" spans="1:6">
       <c r="A228" t="s">
         <v>451</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="229" ht="42" spans="1:6">
+    <row r="229" ht="27" spans="1:6">
       <c r="A229" t="s">
         <v>453</v>
       </c>
@@ -8331,7 +8331,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="230" ht="84" spans="1:6">
+    <row r="230" ht="81" spans="1:6">
       <c r="A230" t="s">
         <v>455</v>
       </c>
@@ -8348,7 +8348,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="231" ht="182" spans="1:6">
+    <row r="231" ht="54" spans="1:6">
       <c r="A231" t="s">
         <v>456</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="232" ht="42" spans="1:6">
+    <row r="232" ht="27" spans="1:6">
       <c r="A232" t="s">
         <v>457</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="233" ht="196" spans="1:6">
+    <row r="233" ht="54" spans="1:6">
       <c r="A233" t="s">
         <v>459</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="234" ht="56" spans="1:6">
+    <row r="234" ht="27" spans="1:6">
       <c r="A234" t="s">
         <v>461</v>
       </c>
@@ -8416,7 +8416,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="235" ht="182" spans="1:6">
+    <row r="235" ht="54" spans="1:6">
       <c r="A235" t="s">
         <v>463</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="236" ht="168" spans="1:6">
+    <row r="236" ht="54" spans="1:6">
       <c r="A236" t="s">
         <v>465</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="237" ht="196" spans="1:6">
+    <row r="237" ht="54" spans="1:6">
       <c r="A237" t="s">
         <v>467</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="238" ht="154" spans="1:6">
+    <row r="238" ht="40.5" spans="1:6">
       <c r="A238" t="s">
         <v>469</v>
       </c>
@@ -8484,7 +8484,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="239" ht="126" spans="1:6">
+    <row r="239" ht="121.5" spans="1:6">
       <c r="A239" t="s">
         <v>470</v>
       </c>
@@ -8501,7 +8501,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="240" ht="98" spans="1:6">
+    <row r="240" ht="94.5" spans="1:6">
       <c r="A240" t="s">
         <v>472</v>
       </c>
@@ -8518,7 +8518,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="241" ht="126" spans="1:6">
+    <row r="241" ht="121.5" spans="1:6">
       <c r="A241" t="s">
         <v>474</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="242" ht="126" spans="1:6">
+    <row r="242" ht="121.5" spans="1:6">
       <c r="A242" t="s">
         <v>476</v>
       </c>
@@ -8552,7 +8552,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="243" ht="196" spans="1:6">
+    <row r="243" ht="54" spans="1:6">
       <c r="A243" t="s">
         <v>478</v>
       </c>
@@ -8569,7 +8569,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="244" ht="112" spans="1:6">
+    <row r="244" ht="108" spans="1:6">
       <c r="A244" t="s">
         <v>480</v>
       </c>
@@ -8589,7 +8589,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="245" ht="238" spans="1:6">
+    <row r="245" ht="81" spans="1:6">
       <c r="A245" t="s">
         <v>483</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="246" ht="112" spans="1:6">
+    <row r="246" ht="108" spans="1:6">
       <c r="A246" t="s">
         <v>485</v>
       </c>
@@ -8626,7 +8626,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="247" ht="140" spans="1:6">
+    <row r="247" ht="135" spans="1:6">
       <c r="A247" t="s">
         <v>488</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="248" ht="140" spans="1:6">
+    <row r="248" ht="54" spans="1:6">
       <c r="A248" t="s">
         <v>490</v>
       </c>
@@ -8660,7 +8660,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="249" ht="126" spans="1:6">
+    <row r="249" ht="54" spans="1:6">
       <c r="A249" t="s">
         <v>492</v>
       </c>
@@ -8677,7 +8677,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="250" ht="154" spans="1:6">
+    <row r="250" ht="148.5" spans="1:6">
       <c r="A250" t="s">
         <v>494</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="251" ht="112" spans="1:6">
+    <row r="251" ht="108" spans="1:6">
       <c r="A251" t="s">
         <v>496</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="252" ht="84" spans="1:6">
+    <row r="252" ht="81" spans="1:6">
       <c r="A252" t="s">
         <v>499</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="253" ht="126" spans="1:6">
+    <row r="253" ht="121.5" spans="1:6">
       <c r="A253" t="s">
         <v>501</v>
       </c>
@@ -8748,7 +8748,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="254" ht="42" spans="1:6">
+    <row r="254" ht="27" spans="1:6">
       <c r="A254" t="s">
         <v>503</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="255" ht="112" spans="1:6">
+    <row r="255" ht="108" spans="1:6">
       <c r="A255" t="s">
         <v>505</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="256" ht="182" spans="1:6">
+    <row r="256" ht="54" spans="1:6">
       <c r="A256" t="s">
         <v>507</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="257" ht="126" spans="1:6">
+    <row r="257" ht="121.5" spans="1:6">
       <c r="A257" t="s">
         <v>509</v>
       </c>
@@ -8816,7 +8816,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="258" ht="182" spans="1:6">
+    <row r="258" ht="54" spans="1:6">
       <c r="A258" t="s">
         <v>511</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="259" ht="84" spans="1:6">
+    <row r="259" ht="81" spans="1:6">
       <c r="A259" t="s">
         <v>513</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="260" ht="112" spans="1:6">
+    <row r="260" ht="108" spans="1:6">
       <c r="A260" t="s">
         <v>514</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="261" ht="84" spans="1:6">
+    <row r="261" ht="81" spans="1:6">
       <c r="A261" t="s">
         <v>517</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="262" ht="224" spans="1:6">
+    <row r="262" ht="67.5" spans="1:6">
       <c r="A262" t="s">
         <v>518</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="263" ht="168" spans="1:6">
+    <row r="263" ht="54" spans="1:6">
       <c r="A263" t="s">
         <v>520</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="264" ht="196" spans="1:6">
+    <row r="264" ht="54" spans="1:6">
       <c r="A264" t="s">
         <v>521</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="265" ht="224" spans="1:6">
+    <row r="265" ht="67.5" spans="1:6">
       <c r="A265" t="s">
         <v>523</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="266" ht="126" spans="1:6">
+    <row r="266" ht="121.5" spans="1:6">
       <c r="A266" t="s">
         <v>525</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="267" ht="112" spans="1:6">
+    <row r="267" ht="108" spans="1:6">
       <c r="A267" t="s">
         <v>528</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="268" ht="266" spans="1:6">
+    <row r="268" ht="81" spans="1:6">
       <c r="A268" t="s">
         <v>530</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="269" ht="112" spans="1:6">
+    <row r="269" ht="108" spans="1:6">
       <c r="A269" t="s">
         <v>532</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="270" ht="196" spans="1:6">
+    <row r="270" ht="67.5" spans="1:6">
       <c r="A270" t="s">
         <v>535</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="271" ht="168" spans="1:6">
+    <row r="271" ht="54" spans="1:6">
       <c r="A271" t="s">
         <v>537</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="272" ht="126" spans="1:6">
+    <row r="272" ht="121.5" spans="1:6">
       <c r="A272" t="s">
         <v>539</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="273" ht="84" spans="1:6">
+    <row r="273" ht="81" spans="1:6">
       <c r="A273" t="s">
         <v>541</v>
       </c>
@@ -9097,7 +9097,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="274" ht="126" spans="1:6">
+    <row r="274" ht="121.5" spans="1:6">
       <c r="A274" t="s">
         <v>542</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="275" ht="126" spans="1:6">
+    <row r="275" ht="121.5" spans="1:6">
       <c r="A275" t="s">
         <v>544</v>
       </c>
@@ -9131,7 +9131,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="276" ht="196" spans="1:6">
+    <row r="276" ht="54" spans="1:6">
       <c r="A276" t="s">
         <v>546</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="277" ht="140" spans="1:6">
+    <row r="277" ht="135" spans="1:6">
       <c r="A277" t="s">
         <v>548</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="278" ht="84" spans="1:6">
+    <row r="278" ht="81" spans="1:6">
       <c r="A278" t="s">
         <v>550</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="279" ht="126" spans="1:6">
+    <row r="279" ht="121.5" spans="1:6">
       <c r="A279" t="s">
         <v>551</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="280" ht="84" spans="1:6">
+    <row r="280" ht="81" spans="1:6">
       <c r="A280" t="s">
         <v>553</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="281" ht="196" spans="1:6">
+    <row r="281" ht="67.5" spans="1:6">
       <c r="A281" t="s">
         <v>554</v>
       </c>
@@ -9233,7 +9233,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="282" ht="42" spans="1:6">
+    <row r="282" ht="27" spans="1:6">
       <c r="A282" t="s">
         <v>556</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="283" ht="28" spans="1:6">
+    <row r="283" ht="27" spans="1:6">
       <c r="A283" t="s">
         <v>557</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="284" ht="56" spans="1:6">
+    <row r="284" ht="27" spans="1:6">
       <c r="A284" t="s">
         <v>558</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="285" ht="70" spans="1:6">
+    <row r="285" ht="40.5" spans="1:6">
       <c r="A285" t="s">
         <v>560</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="286" ht="28" spans="1:6">
+    <row r="286" ht="27" spans="1:6">
       <c r="A286" t="s">
         <v>562</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="287" ht="70" spans="1:6">
+    <row r="287" ht="40.5" spans="1:6">
       <c r="A287" t="s">
         <v>563</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="288" ht="70" spans="1:6">
+    <row r="288" ht="27" spans="1:6">
       <c r="A288" t="s">
         <v>565</v>
       </c>
@@ -9352,7 +9352,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="289" ht="140" spans="1:6">
+    <row r="289" ht="135" spans="1:6">
       <c r="A289" t="s">
         <v>567</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="290" ht="56" spans="1:6">
+    <row r="290" ht="27" spans="1:6">
       <c r="A290" t="s">
         <v>569</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="291" ht="28" spans="1:6">
+    <row r="291" ht="27" spans="1:6">
       <c r="A291" t="s">
         <v>571</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="292" ht="210" spans="1:6">
+    <row r="292" ht="67.5" spans="1:6">
       <c r="A292" t="s">
         <v>572</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="293" ht="56" spans="1:6">
+    <row r="293" ht="40.5" spans="1:6">
       <c r="A293" t="s">
         <v>574</v>
       </c>
@@ -9437,7 +9437,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="294" ht="210" spans="1:6">
+    <row r="294" ht="67.5" spans="1:6">
       <c r="A294" t="s">
         <v>576</v>
       </c>
@@ -9454,7 +9454,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="295" ht="238" spans="1:6">
+    <row r="295" ht="81" spans="1:6">
       <c r="A295" t="s">
         <v>578</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="296" ht="42" spans="1:6">
+    <row r="296" ht="27" spans="1:6">
       <c r="A296" t="s">
         <v>580</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="297" ht="112" spans="1:6">
+    <row r="297" ht="108" spans="1:6">
       <c r="A297" t="s">
         <v>582</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="298" ht="98" spans="1:6">
+    <row r="298" ht="94.5" spans="1:6">
       <c r="A298" t="s">
         <v>584</v>
       </c>
@@ -9525,7 +9525,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="299" ht="56" spans="1:6">
+    <row r="299" ht="27" spans="1:6">
       <c r="A299" t="s">
         <v>587</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="300" ht="154" spans="1:6">
+    <row r="300" ht="40.5" spans="1:6">
       <c r="A300" t="s">
         <v>589</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="301" ht="252" spans="1:6">
+    <row r="301" ht="67.5" spans="1:6">
       <c r="A301" t="s">
         <v>590</v>
       </c>
@@ -9576,7 +9576,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="302" ht="112" spans="1:6">
+    <row r="302" ht="108" spans="1:6">
       <c r="A302" t="s">
         <v>592</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="303" ht="238" spans="1:6">
+    <row r="303" ht="94.5" spans="1:6">
       <c r="A303" t="s">
         <v>594</v>
       </c>
@@ -9610,7 +9610,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="304" ht="112" spans="1:6">
+    <row r="304" ht="108" spans="1:6">
       <c r="A304" t="s">
         <v>596</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="305" ht="98" spans="1:6">
+    <row r="305" ht="94.5" spans="1:6">
       <c r="A305" t="s">
         <v>599</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="306" ht="112" spans="1:6">
+    <row r="306" ht="108" spans="1:6">
       <c r="A306" t="s">
         <v>602</v>
       </c>
@@ -9670,7 +9670,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="307" ht="112" spans="1:6">
+    <row r="307" ht="108" spans="1:6">
       <c r="A307" t="s">
         <v>605</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="308" ht="196" spans="1:6">
+    <row r="308" ht="54" spans="1:6">
       <c r="A308" t="s">
         <v>608</v>
       </c>
@@ -9707,7 +9707,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="309" ht="112" spans="1:6">
+    <row r="309" ht="108" spans="1:6">
       <c r="A309" t="s">
         <v>610</v>
       </c>
@@ -9727,7 +9727,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="310" ht="112" spans="1:6">
+    <row r="310" ht="108" spans="1:6">
       <c r="A310" t="s">
         <v>613</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="311" ht="238" spans="1:6">
+    <row r="311" ht="202.5" spans="1:6">
       <c r="A311" t="s">
         <v>616</v>
       </c>
@@ -9764,7 +9764,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="312" ht="196" spans="1:6">
+    <row r="312" ht="54" spans="1:6">
       <c r="A312" t="s">
         <v>618</v>
       </c>
@@ -9781,7 +9781,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="313" ht="126" spans="1:6">
+    <row r="313" ht="121.5" spans="1:6">
       <c r="A313" t="s">
         <v>620</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="314" ht="210" spans="1:6">
+    <row r="314" ht="67.5" spans="1:6">
       <c r="A314" t="s">
         <v>622</v>
       </c>
@@ -9815,7 +9815,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="315" ht="182" spans="1:6">
+    <row r="315" ht="175.5" spans="1:6">
       <c r="A315" t="s">
         <v>624</v>
       </c>
@@ -9835,7 +9835,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="316" ht="28" spans="1:6">
+    <row r="316" ht="27" spans="1:6">
       <c r="A316" t="s">
         <v>627</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="317" ht="28" spans="1:6">
+    <row r="317" ht="27" spans="1:6">
       <c r="A317" t="s">
         <v>629</v>
       </c>
@@ -9869,7 +9869,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="318" ht="84" spans="1:6">
+    <row r="318" ht="81" spans="1:6">
       <c r="A318" t="s">
         <v>631</v>
       </c>
@@ -9886,7 +9886,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="319" ht="210" spans="1:6">
+    <row r="319" ht="67.5" spans="1:6">
       <c r="A319" t="s">
         <v>633</v>
       </c>
@@ -9903,7 +9903,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="320" ht="84" spans="1:6">
+    <row r="320" ht="40.5" spans="1:6">
       <c r="A320" t="s">
         <v>635</v>
       </c>
@@ -9920,7 +9920,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="321" ht="84" spans="1:6">
+    <row r="321" ht="81" spans="1:6">
       <c r="A321" t="s">
         <v>637</v>
       </c>
@@ -9937,7 +9937,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="322" ht="168" spans="1:6">
+    <row r="322" ht="54" spans="1:6">
       <c r="A322" t="s">
         <v>639</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="323" ht="56" spans="1:6">
+    <row r="323" ht="27" spans="1:6">
       <c r="A323" t="s">
         <v>641</v>
       </c>
@@ -9971,7 +9971,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="324" ht="182" spans="1:6">
+    <row r="324" ht="54" spans="1:6">
       <c r="A324" t="s">
         <v>643</v>
       </c>
@@ -9988,7 +9988,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="325" ht="84" spans="1:6">
+    <row r="325" ht="81" spans="1:6">
       <c r="A325" t="s">
         <v>644</v>
       </c>
@@ -10005,7 +10005,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="326" ht="42" spans="1:6">
+    <row r="326" ht="27" spans="1:6">
       <c r="A326" t="s">
         <v>645</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="327" ht="70" spans="1:6">
+    <row r="327" ht="54" spans="1:6">
       <c r="A327" t="s">
         <v>647</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="328" ht="196" spans="1:6">
+    <row r="328" ht="54" spans="1:6">
       <c r="A328" t="s">
         <v>649</v>
       </c>
@@ -10059,7 +10059,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="329" ht="70" spans="1:6">
+    <row r="329" ht="54" spans="1:6">
       <c r="A329" t="s">
         <v>651</v>
       </c>
@@ -10079,7 +10079,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="330" ht="182" spans="1:6">
+    <row r="330" ht="54" spans="1:6">
       <c r="A330" t="s">
         <v>654</v>
       </c>
@@ -10096,7 +10096,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="331" ht="182" spans="1:6">
+    <row r="331" ht="54" spans="1:6">
       <c r="A331" t="s">
         <v>656</v>
       </c>
@@ -10113,7 +10113,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="332" ht="168" spans="1:6">
+    <row r="332" ht="54" spans="1:6">
       <c r="A332" t="s">
         <v>658</v>
       </c>
@@ -10130,7 +10130,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="333" ht="182" spans="1:6">
+    <row r="333" ht="54" spans="1:6">
       <c r="A333" t="s">
         <v>660</v>
       </c>
@@ -10147,7 +10147,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="334" ht="56" spans="1:6">
+    <row r="334" ht="27" spans="1:6">
       <c r="A334" t="s">
         <v>662</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="335" ht="182" spans="1:6">
+    <row r="335" ht="54" spans="1:6">
       <c r="A335" t="s">
         <v>664</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="336" ht="182" spans="1:6">
+    <row r="336" ht="54" spans="1:6">
       <c r="A336" t="s">
         <v>666</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="337" ht="84" spans="1:6">
+    <row r="337" ht="81" spans="1:6">
       <c r="A337" t="s">
         <v>668</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="338" ht="42" spans="1:6">
+    <row r="338" ht="27" spans="1:6">
       <c r="A338" t="s">
         <v>669</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="339" ht="42" spans="1:6">
+    <row r="339" ht="27" spans="1:6">
       <c r="A339" t="s">
         <v>671</v>
       </c>
@@ -10249,7 +10249,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="340" ht="182" spans="1:6">
+    <row r="340" ht="54" spans="1:6">
       <c r="A340" t="s">
         <v>672</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="341" ht="168" spans="1:6">
+    <row r="341" ht="54" spans="1:6">
       <c r="A341" t="s">
         <v>674</v>
       </c>
@@ -10283,7 +10283,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="342" ht="224" spans="1:6">
+    <row r="342" ht="67.5" spans="1:6">
       <c r="A342" t="s">
         <v>676</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="343" ht="112" spans="1:6">
+    <row r="343" ht="108" spans="1:6">
       <c r="A343" t="s">
         <v>678</v>
       </c>
@@ -10317,7 +10317,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="344" ht="112" spans="1:6">
+    <row r="344" ht="94.5" spans="1:6">
       <c r="A344" t="s">
         <v>680</v>
       </c>
@@ -10337,7 +10337,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="345" ht="182" spans="1:6">
+    <row r="345" ht="54" spans="1:6">
       <c r="A345" t="s">
         <v>683</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="346" ht="196" spans="1:6">
+    <row r="346" ht="54" spans="1:6">
       <c r="A346" t="s">
         <v>685</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="347" ht="84" spans="1:6">
+    <row r="347" ht="40.5" spans="1:6">
       <c r="A347" t="s">
         <v>687</v>
       </c>
@@ -10388,7 +10388,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="348" ht="224" spans="1:6">
+    <row r="348" ht="81" spans="1:6">
       <c r="A348" t="s">
         <v>689</v>
       </c>
@@ -10405,7 +10405,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="349" ht="182" spans="1:6">
+    <row r="349" ht="54" spans="1:6">
       <c r="A349" t="s">
         <v>691</v>
       </c>
@@ -10422,7 +10422,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="350" ht="112" spans="1:6">
+    <row r="350" ht="108" spans="1:6">
       <c r="A350" t="s">
         <v>693</v>
       </c>
@@ -10439,7 +10439,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="351" ht="84" spans="1:6">
+    <row r="351" ht="81" spans="1:6">
       <c r="A351" t="s">
         <v>695</v>
       </c>
@@ -10456,7 +10456,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="352" ht="84" spans="1:6">
+    <row r="352" ht="81" spans="1:6">
       <c r="A352" t="s">
         <v>697</v>
       </c>
@@ -10473,7 +10473,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="353" ht="140" spans="1:6">
+    <row r="353" ht="135" spans="1:6">
       <c r="A353" t="s">
         <v>699</v>
       </c>
